--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360490</v>
+        <v>122359111</v>
       </c>
       <c r="B2" t="n">
-        <v>79755</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494402</v>
+        <v>494496</v>
       </c>
       <c r="R2" t="n">
-        <v>7006360</v>
+        <v>7006482</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -758,6 +763,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,7 +817,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361274</v>
+        <v>122359691</v>
       </c>
       <c r="B3" t="n">
         <v>78645</v>
@@ -847,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494472</v>
+        <v>494410</v>
       </c>
       <c r="R3" t="n">
-        <v>7006382</v>
+        <v>7006434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,11 +893,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,7 +944,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122355540</v>
+        <v>122361005</v>
       </c>
       <c r="B4" t="n">
         <v>78645</v>
@@ -975,17 +980,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494535</v>
+        <v>494444</v>
       </c>
       <c r="R4" t="n">
-        <v>7006574</v>
+        <v>7006335</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1066,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122355645</v>
+        <v>122354497</v>
       </c>
       <c r="B5" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,31 +1087,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1120,13 +1121,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494521</v>
+        <v>494602</v>
       </c>
       <c r="R5" t="n">
-        <v>7006584</v>
+        <v>7006702</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1158,6 +1159,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1170,6 +1176,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1213,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122360161</v>
+        <v>122364318</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,37 +1229,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494380</v>
+        <v>494511</v>
       </c>
       <c r="R6" t="n">
-        <v>7006419</v>
+        <v>7006626</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1301,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,24 +1318,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1358,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122355822</v>
+        <v>122361274</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,47 +1374,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494487</v>
+        <v>494472</v>
       </c>
       <c r="R7" t="n">
-        <v>7006560</v>
+        <v>7006382</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,7 +1438,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,12 +1467,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1461,10 +1490,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122357658</v>
+        <v>122364212</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,16 +1506,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1495,6 +1524,8 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1507,17 +1538,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494515</v>
+        <v>494582</v>
       </c>
       <c r="R8" t="n">
-        <v>7006545</v>
+        <v>7006726</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1551,7 +1582,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,6 +1599,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1580,12 +1616,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1603,7 +1639,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122364318</v>
+        <v>122355822</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1637,27 +1673,29 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494511</v>
+        <v>494487</v>
       </c>
       <c r="R9" t="n">
-        <v>7006626</v>
+        <v>7006560</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1691,7 +1729,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,11 +1744,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1748,10 +1781,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359691</v>
+        <v>122355606</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1764,34 +1797,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494410</v>
+        <v>494524</v>
       </c>
       <c r="R10" t="n">
-        <v>7006434</v>
+        <v>7006571</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1826,6 +1869,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1852,12 +1900,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1875,10 +1923,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122355606</v>
+        <v>122359011</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>78645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1891,44 +1939,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494524</v>
+        <v>494502</v>
       </c>
       <c r="R11" t="n">
-        <v>7006571</v>
+        <v>7006489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1963,11 +2001,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1994,12 +2027,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2017,10 +2050,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122361219</v>
+        <v>122357658</v>
       </c>
       <c r="B12" t="n">
-        <v>79727</v>
+        <v>57390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2033,27 +2066,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2062,13 +2100,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494464</v>
+        <v>494515</v>
       </c>
       <c r="R12" t="n">
-        <v>7006354</v>
+        <v>7006545</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2102,7 +2140,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,22 +2159,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2303,10 +2341,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122359011</v>
+        <v>122360500</v>
       </c>
       <c r="B14" t="n">
-        <v>78645</v>
+        <v>79762</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2315,38 +2353,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494502</v>
+        <v>494402</v>
       </c>
       <c r="R14" t="n">
-        <v>7006489</v>
+        <v>7006360</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2397,22 +2440,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2430,10 +2473,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122361005</v>
+        <v>122361219</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2446,37 +2489,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494444</v>
+        <v>494464</v>
       </c>
       <c r="R15" t="n">
-        <v>7006335</v>
+        <v>7006354</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2508,6 +2556,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2524,22 +2577,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2557,7 +2610,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122360599</v>
+        <v>122361119</v>
       </c>
       <c r="B16" t="n">
         <v>79726</v>
@@ -2591,19 +2644,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494411</v>
+        <v>494460</v>
       </c>
       <c r="R16" t="n">
-        <v>7006366</v>
+        <v>7006357</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2637,7 +2695,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2689,10 +2747,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122355933</v>
+        <v>122360490</v>
       </c>
       <c r="B17" t="n">
-        <v>78645</v>
+        <v>79755</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2701,41 +2759,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494462</v>
+        <v>494402</v>
       </c>
       <c r="R17" t="n">
-        <v>7006583</v>
+        <v>7006360</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2783,22 +2846,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2816,10 +2879,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122359111</v>
+        <v>122364729</v>
       </c>
       <c r="B18" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2832,16 +2895,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2850,6 +2913,8 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2862,17 +2927,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494496</v>
+        <v>494499</v>
       </c>
       <c r="R18" t="n">
-        <v>7006482</v>
+        <v>7006492</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2906,7 +2971,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2923,24 +2988,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2958,10 +3028,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122361119</v>
+        <v>122360218</v>
       </c>
       <c r="B19" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2974,42 +3044,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494460</v>
+        <v>494394</v>
       </c>
       <c r="R19" t="n">
-        <v>7006357</v>
+        <v>7006412</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3041,11 +3106,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3062,22 +3122,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3095,10 +3155,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122364212</v>
+        <v>122360161</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>79726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3111,49 +3171,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494582</v>
+        <v>494380</v>
       </c>
       <c r="R20" t="n">
-        <v>7006726</v>
+        <v>7006419</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3187,7 +3235,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3204,29 +3252,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3244,10 +3287,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122360500</v>
+        <v>122357683</v>
       </c>
       <c r="B21" t="n">
-        <v>79762</v>
+        <v>90797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3256,31 +3299,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3289,10 +3332,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494402</v>
+        <v>494501</v>
       </c>
       <c r="R21" t="n">
-        <v>7006360</v>
+        <v>7006553</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3343,22 +3386,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3376,10 +3419,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122357683</v>
+        <v>122357863</v>
       </c>
       <c r="B22" t="n">
-        <v>90797</v>
+        <v>57527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3392,27 +3435,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3421,10 +3473,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494501</v>
+        <v>494497</v>
       </c>
       <c r="R22" t="n">
-        <v>7006553</v>
+        <v>7006523</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3471,26 +3523,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3508,7 +3540,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122360218</v>
+        <v>122355933</v>
       </c>
       <c r="B23" t="n">
         <v>78645</v>
@@ -3548,13 +3580,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494394</v>
+        <v>494462</v>
       </c>
       <c r="R23" t="n">
-        <v>7006412</v>
+        <v>7006583</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3635,10 +3667,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122354497</v>
+        <v>122360113</v>
       </c>
       <c r="B24" t="n">
-        <v>57390</v>
+        <v>79755</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3647,51 +3679,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494602</v>
+        <v>494392</v>
       </c>
       <c r="R24" t="n">
-        <v>7006702</v>
+        <v>7006448</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3723,11 +3750,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3744,22 +3766,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3777,10 +3799,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122360113</v>
+        <v>122355540</v>
       </c>
       <c r="B25" t="n">
-        <v>79755</v>
+        <v>78645</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3789,43 +3811,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494392</v>
+        <v>494535</v>
       </c>
       <c r="R25" t="n">
-        <v>7006448</v>
+        <v>7006574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3876,22 +3893,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3909,10 +3926,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122364729</v>
+        <v>122361037</v>
       </c>
       <c r="B26" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3925,49 +3942,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494499</v>
+        <v>494456</v>
       </c>
       <c r="R26" t="n">
-        <v>7006492</v>
+        <v>7006360</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3999,11 +4004,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4018,11 +4018,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4035,12 +4030,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4058,10 +4053,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122357863</v>
+        <v>122360599</v>
       </c>
       <c r="B27" t="n">
-        <v>57527</v>
+        <v>79726</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4074,48 +4069,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494497</v>
+        <v>494411</v>
       </c>
       <c r="R27" t="n">
-        <v>7006523</v>
+        <v>7006366</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4150,6 +4131,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4162,6 +4148,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4179,10 +4185,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122361037</v>
+        <v>122355645</v>
       </c>
       <c r="B28" t="n">
-        <v>78645</v>
+        <v>57527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4195,37 +4201,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494456</v>
+        <v>494521</v>
       </c>
       <c r="R28" t="n">
-        <v>7006360</v>
+        <v>7006584</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4269,26 +4289,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122355822</v>
+        <v>122359011</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1655,47 +1655,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494487</v>
+        <v>494502</v>
       </c>
       <c r="R9" t="n">
-        <v>7006560</v>
+        <v>7006489</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1727,11 +1717,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1758,12 +1743,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1781,10 +1766,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122355606</v>
+        <v>122355822</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1797,16 +1782,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1817,7 +1802,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1827,17 +1812,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494524</v>
+        <v>494487</v>
       </c>
       <c r="R10" t="n">
-        <v>7006571</v>
+        <v>7006560</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1871,7 +1856,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1900,12 +1885,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1923,10 +1908,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122359011</v>
+        <v>122355606</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1939,34 +1924,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494502</v>
+        <v>494524</v>
       </c>
       <c r="R11" t="n">
-        <v>7006489</v>
+        <v>7006571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2001,6 +1996,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122360161</v>
+        <v>122357683</v>
       </c>
       <c r="B20" t="n">
-        <v>79726</v>
+        <v>90797</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3171,37 +3171,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494380</v>
+        <v>494501</v>
       </c>
       <c r="R20" t="n">
-        <v>7006419</v>
+        <v>7006553</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3233,11 +3238,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3254,22 +3254,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122357683</v>
+        <v>122357863</v>
       </c>
       <c r="B21" t="n">
-        <v>90797</v>
+        <v>57527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3303,27 +3303,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3332,10 +3341,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494501</v>
+        <v>494497</v>
       </c>
       <c r="R21" t="n">
-        <v>7006553</v>
+        <v>7006523</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3382,26 +3391,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3419,10 +3408,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122357863</v>
+        <v>122360161</v>
       </c>
       <c r="B22" t="n">
-        <v>57527</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3435,51 +3424,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494497</v>
+        <v>494380</v>
       </c>
       <c r="R22" t="n">
-        <v>7006523</v>
+        <v>7006419</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3511,6 +3486,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3523,6 +3503,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -4304,6 +4304,1331 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122405719</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>494740</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7006719</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122406516</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>494604</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7006665</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122406373</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>494674</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7006716</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122407975</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>494572</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7006632</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122407432</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>494548</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7006529</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122406983</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>494621</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7006636</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122407671</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>494534</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7006518</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov granstam.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122407942</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>494566</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7006630</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122406150</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>494722</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7006694</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122408149</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90807</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>494574</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7006638</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359111</v>
+        <v>122364729</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,6 +709,8 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -721,17 +723,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494496</v>
+        <v>494499</v>
       </c>
       <c r="R2" t="n">
-        <v>7006482</v>
+        <v>7006492</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,24 +784,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +824,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359691</v>
+        <v>122361219</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>79728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,37 +840,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494410</v>
+        <v>494464</v>
       </c>
       <c r="R3" t="n">
-        <v>7006434</v>
+        <v>7006354</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,6 +907,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -911,22 +928,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +961,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361005</v>
+        <v>122357658</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,37 +977,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494444</v>
+        <v>494515</v>
       </c>
       <c r="R4" t="n">
-        <v>7006335</v>
+        <v>7006545</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,6 +1049,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1048,12 +1080,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1103,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122354497</v>
+        <v>122355933</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,44 +1119,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494602</v>
+        <v>494462</v>
       </c>
       <c r="R5" t="n">
-        <v>7006702</v>
+        <v>7006583</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1159,11 +1181,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1190,12 +1207,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1213,10 +1230,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122364318</v>
+        <v>122360218</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1229,45 +1246,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494511</v>
+        <v>494394</v>
       </c>
       <c r="R6" t="n">
-        <v>7006626</v>
+        <v>7006412</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1299,11 +1308,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1318,11 +1322,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1335,12 +1334,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1358,10 +1357,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122361274</v>
+        <v>122359111</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,37 +1373,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494472</v>
+        <v>494496</v>
       </c>
       <c r="R7" t="n">
-        <v>7006382</v>
+        <v>7006482</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1438,7 +1447,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1457,22 +1466,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1490,10 +1499,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122364212</v>
+        <v>122360599</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1506,49 +1515,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494582</v>
+        <v>494411</v>
       </c>
       <c r="R8" t="n">
-        <v>7006726</v>
+        <v>7006366</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1582,7 +1579,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,29 +1596,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1639,10 +1631,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359011</v>
+        <v>122364318</v>
       </c>
       <c r="B9" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1655,37 +1647,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494502</v>
+        <v>494511</v>
       </c>
       <c r="R9" t="n">
-        <v>7006489</v>
+        <v>7006626</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1717,6 +1717,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1731,6 +1736,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1743,12 +1753,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1766,7 +1776,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122355822</v>
+        <v>122364537</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1800,6 +1810,8 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -1812,17 +1824,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494487</v>
+        <v>494454</v>
       </c>
       <c r="R10" t="n">
-        <v>7006560</v>
+        <v>7006579</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1856,7 +1868,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1871,6 +1883,11 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1908,10 +1925,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122355606</v>
+        <v>122360161</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>79727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1924,47 +1941,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494524</v>
+        <v>494380</v>
       </c>
       <c r="R11" t="n">
-        <v>7006571</v>
+        <v>7006419</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1998,7 +2005,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2017,22 +2024,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2050,10 +2057,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357658</v>
+        <v>122359691</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2066,44 +2073,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494515</v>
+        <v>494410</v>
       </c>
       <c r="R12" t="n">
-        <v>7006545</v>
+        <v>7006434</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2138,11 +2135,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2169,12 +2161,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2192,10 +2184,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122364537</v>
+        <v>122354497</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2208,16 +2200,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2226,8 +2218,6 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -2240,17 +2230,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494454</v>
+        <v>494602</v>
       </c>
       <c r="R13" t="n">
-        <v>7006579</v>
+        <v>7006702</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2284,7 +2274,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2299,11 +2289,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2344,7 +2329,7 @@
         <v>122360500</v>
       </c>
       <c r="B14" t="n">
-        <v>79762</v>
+        <v>79763</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2473,10 +2458,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122361219</v>
+        <v>122357863</v>
       </c>
       <c r="B15" t="n">
-        <v>79727</v>
+        <v>57527</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2489,27 +2474,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2518,13 +2512,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494464</v>
+        <v>494497</v>
       </c>
       <c r="R15" t="n">
-        <v>7006354</v>
+        <v>7006523</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2556,11 +2550,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2573,26 +2562,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2610,10 +2579,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122361119</v>
+        <v>122355822</v>
       </c>
       <c r="B16" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2626,27 +2595,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2655,13 +2629,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494460</v>
+        <v>494487</v>
       </c>
       <c r="R16" t="n">
-        <v>7006357</v>
+        <v>7006560</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2695,7 +2669,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2714,22 +2688,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2750,7 +2724,7 @@
         <v>122360490</v>
       </c>
       <c r="B17" t="n">
-        <v>79755</v>
+        <v>79756</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2879,10 +2853,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122364729</v>
+        <v>122355540</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2895,49 +2869,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494499</v>
+        <v>494535</v>
       </c>
       <c r="R18" t="n">
-        <v>7006492</v>
+        <v>7006574</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2969,11 +2931,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2988,11 +2945,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3005,12 +2957,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3028,10 +2980,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122360218</v>
+        <v>122361119</v>
       </c>
       <c r="B19" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3044,37 +2996,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494394</v>
+        <v>494460</v>
       </c>
       <c r="R19" t="n">
-        <v>7006412</v>
+        <v>7006357</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3106,6 +3063,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3122,22 +3084,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3155,10 +3117,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122357683</v>
+        <v>122361005</v>
       </c>
       <c r="B20" t="n">
-        <v>90797</v>
+        <v>78646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3171,42 +3133,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494501</v>
+        <v>494444</v>
       </c>
       <c r="R20" t="n">
-        <v>7006553</v>
+        <v>7006335</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3264,12 +3221,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3287,10 +3244,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122357863</v>
+        <v>122361274</v>
       </c>
       <c r="B21" t="n">
-        <v>57527</v>
+        <v>78646</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3303,48 +3260,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494497</v>
+        <v>494472</v>
       </c>
       <c r="R21" t="n">
-        <v>7006523</v>
+        <v>7006382</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3379,6 +3322,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3391,6 +3339,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3408,10 +3376,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122360161</v>
+        <v>122357683</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>90807</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3424,37 +3392,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494380</v>
+        <v>494501</v>
       </c>
       <c r="R22" t="n">
-        <v>7006419</v>
+        <v>7006553</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3486,11 +3459,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3507,22 +3475,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3540,10 +3508,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122355933</v>
+        <v>122364212</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3556,37 +3524,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494462</v>
+        <v>494582</v>
       </c>
       <c r="R23" t="n">
-        <v>7006583</v>
+        <v>7006726</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3618,6 +3598,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3632,6 +3617,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3644,12 +3634,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3667,10 +3657,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122360113</v>
+        <v>122355606</v>
       </c>
       <c r="B24" t="n">
-        <v>79755</v>
+        <v>57390</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3679,43 +3669,48 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494392</v>
+        <v>494524</v>
       </c>
       <c r="R24" t="n">
-        <v>7006448</v>
+        <v>7006571</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3750,6 +3745,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3766,22 +3766,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122355540</v>
+        <v>122361037</v>
       </c>
       <c r="B25" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3835,17 +3835,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494535</v>
+        <v>494456</v>
       </c>
       <c r="R25" t="n">
-        <v>7006574</v>
+        <v>7006360</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122361037</v>
+        <v>122359011</v>
       </c>
       <c r="B26" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3966,13 +3966,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494456</v>
+        <v>494502</v>
       </c>
       <c r="R26" t="n">
-        <v>7006360</v>
+        <v>7006489</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122360599</v>
+        <v>122360113</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>79756</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4065,38 +4065,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494411</v>
+        <v>494392</v>
       </c>
       <c r="R27" t="n">
-        <v>7006366</v>
+        <v>7006448</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4129,11 +4134,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4306,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122405719</v>
+        <v>122407942</v>
       </c>
       <c r="B29" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4322,34 +4322,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494740</v>
+        <v>494566</v>
       </c>
       <c r="R29" t="n">
-        <v>7006719</v>
+        <v>7006630</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4384,6 +4394,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4400,22 +4415,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4433,10 +4448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122406516</v>
+        <v>122407975</v>
       </c>
       <c r="B30" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4473,10 +4488,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494604</v>
+        <v>494572</v>
       </c>
       <c r="R30" t="n">
-        <v>7006665</v>
+        <v>7006632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4563,7 +4578,7 @@
         <v>122406373</v>
       </c>
       <c r="B31" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4687,7 +4702,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122407975</v>
+        <v>122406983</v>
       </c>
       <c r="B32" t="n">
         <v>78646</v>
@@ -4727,10 +4742,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494572</v>
+        <v>494621</v>
       </c>
       <c r="R32" t="n">
-        <v>7006632</v>
+        <v>7006636</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4814,10 +4829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122407432</v>
+        <v>122405719</v>
       </c>
       <c r="B33" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4830,44 +4845,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494548</v>
+        <v>494740</v>
       </c>
       <c r="R33" t="n">
-        <v>7006529</v>
+        <v>7006719</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4902,11 +4907,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4933,12 +4933,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4956,10 +4956,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122406983</v>
+        <v>122406150</v>
       </c>
       <c r="B34" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494621</v>
+        <v>494722</v>
       </c>
       <c r="R34" t="n">
-        <v>7006636</v>
+        <v>7006694</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407671</v>
+        <v>122406516</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5099,44 +5099,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494534</v>
+        <v>494604</v>
       </c>
       <c r="R35" t="n">
-        <v>7006518</v>
+        <v>7006665</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5171,11 +5161,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5202,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5225,10 +5210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122407942</v>
+        <v>122407432</v>
       </c>
       <c r="B36" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5241,16 +5226,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5261,7 +5246,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5271,14 +5256,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494566</v>
+        <v>494548</v>
       </c>
       <c r="R36" t="n">
-        <v>7006630</v>
+        <v>7006529</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5315,7 +5300,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5334,22 +5319,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5367,10 +5352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122406150</v>
+        <v>122408149</v>
       </c>
       <c r="B37" t="n">
-        <v>78645</v>
+        <v>90807</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5383,34 +5368,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494722</v>
+        <v>494574</v>
       </c>
       <c r="R37" t="n">
-        <v>7006694</v>
+        <v>7006638</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5445,6 +5435,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5471,12 +5466,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5494,10 +5489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122408149</v>
+        <v>122407671</v>
       </c>
       <c r="B38" t="n">
-        <v>90807</v>
+        <v>57374</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5510,39 +5505,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494574</v>
+        <v>494534</v>
       </c>
       <c r="R38" t="n">
-        <v>7006638</v>
+        <v>7006518</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Färska ringhack på en relativt grov granstam.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122364729</v>
+        <v>122360161</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494499</v>
+        <v>494380</v>
       </c>
       <c r="R2" t="n">
-        <v>7006492</v>
+        <v>7006419</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,29 +772,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -824,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361219</v>
+        <v>122357683</v>
       </c>
       <c r="B3" t="n">
-        <v>79728</v>
+        <v>90807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,27 +823,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -869,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494464</v>
+        <v>494501</v>
       </c>
       <c r="R3" t="n">
-        <v>7006354</v>
+        <v>7006553</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,11 +890,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -928,22 +906,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -961,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122357658</v>
+        <v>122360599</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>79727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,44 +955,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494515</v>
+        <v>494411</v>
       </c>
       <c r="R4" t="n">
-        <v>7006545</v>
+        <v>7006366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1051,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,22 +1038,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1103,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122355933</v>
+        <v>122357863</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>57527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,37 +1087,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494462</v>
+        <v>494497</v>
       </c>
       <c r="R5" t="n">
-        <v>7006583</v>
+        <v>7006523</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1193,26 +1175,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1230,10 +1192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122360218</v>
+        <v>122355645</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>57527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1246,34 +1208,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494394</v>
+        <v>494521</v>
       </c>
       <c r="R6" t="n">
-        <v>7006412</v>
+        <v>7006584</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,26 +1296,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1357,10 +1313,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359111</v>
+        <v>122360218</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,47 +1329,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494496</v>
+        <v>494394</v>
       </c>
       <c r="R7" t="n">
-        <v>7006482</v>
+        <v>7006412</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1445,11 +1391,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1466,22 +1407,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1499,10 +1440,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122360599</v>
+        <v>122364318</v>
       </c>
       <c r="B8" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1515,37 +1456,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494411</v>
+        <v>494511</v>
       </c>
       <c r="R8" t="n">
-        <v>7006366</v>
+        <v>7006626</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1579,7 +1528,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1596,24 +1545,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1631,7 +1585,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122364318</v>
+        <v>122364537</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1669,20 +1623,24 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494511</v>
+        <v>494454</v>
       </c>
       <c r="R9" t="n">
-        <v>7006626</v>
+        <v>7006579</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1719,7 +1677,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1776,10 +1734,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122364537</v>
+        <v>122361037</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1792,49 +1750,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494454</v>
+        <v>494456</v>
       </c>
       <c r="R10" t="n">
-        <v>7006579</v>
+        <v>7006360</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1866,11 +1812,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1885,11 +1826,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1902,12 +1838,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1925,10 +1861,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122360161</v>
+        <v>122361219</v>
       </c>
       <c r="B11" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1941,37 +1877,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494380</v>
+        <v>494464</v>
       </c>
       <c r="R11" t="n">
-        <v>7006419</v>
+        <v>7006354</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2005,7 +1946,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2034,12 +1975,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2326,10 +2267,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122360500</v>
+        <v>122364212</v>
       </c>
       <c r="B14" t="n">
-        <v>79763</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2338,46 +2279,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494402</v>
+        <v>494582</v>
       </c>
       <c r="R14" t="n">
-        <v>7006360</v>
+        <v>7006726</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2409,6 +2357,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2423,24 +2376,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2458,10 +2416,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357863</v>
+        <v>122359011</v>
       </c>
       <c r="B15" t="n">
-        <v>57527</v>
+        <v>78646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2474,48 +2432,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494497</v>
+        <v>494502</v>
       </c>
       <c r="R15" t="n">
-        <v>7006523</v>
+        <v>7006489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2562,6 +2506,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2579,10 +2543,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122355822</v>
+        <v>122355540</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2595,47 +2559,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494487</v>
+        <v>494535</v>
       </c>
       <c r="R16" t="n">
-        <v>7006560</v>
+        <v>7006574</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2667,11 +2621,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2698,12 +2647,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2721,7 +2670,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122360490</v>
+        <v>122360113</v>
       </c>
       <c r="B17" t="n">
         <v>79756</v>
@@ -2766,13 +2715,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494402</v>
+        <v>494392</v>
       </c>
       <c r="R17" t="n">
-        <v>7006360</v>
+        <v>7006448</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2853,7 +2802,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122355540</v>
+        <v>122361274</v>
       </c>
       <c r="B18" t="n">
         <v>78646</v>
@@ -2889,14 +2838,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494535</v>
+        <v>494472</v>
       </c>
       <c r="R18" t="n">
-        <v>7006574</v>
+        <v>7006382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2929,6 +2878,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2980,10 +2934,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122361119</v>
+        <v>122357658</v>
       </c>
       <c r="B19" t="n">
-        <v>79727</v>
+        <v>57390</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2996,27 +2950,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3025,13 +2984,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494460</v>
+        <v>494515</v>
       </c>
       <c r="R19" t="n">
-        <v>7006357</v>
+        <v>7006545</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3065,7 +3024,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3084,22 +3043,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3117,10 +3076,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122361005</v>
+        <v>122355822</v>
       </c>
       <c r="B20" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3133,34 +3092,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494444</v>
+        <v>494487</v>
       </c>
       <c r="R20" t="n">
-        <v>7006335</v>
+        <v>7006560</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3195,6 +3164,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3221,12 +3195,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3244,10 +3218,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122361274</v>
+        <v>122360500</v>
       </c>
       <c r="B21" t="n">
-        <v>78646</v>
+        <v>79763</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3256,38 +3230,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494472</v>
+        <v>494402</v>
       </c>
       <c r="R21" t="n">
-        <v>7006382</v>
+        <v>7006360</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3322,11 +3301,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3343,22 +3317,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3376,10 +3350,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122357683</v>
+        <v>122355606</v>
       </c>
       <c r="B22" t="n">
-        <v>90807</v>
+        <v>57390</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3392,39 +3366,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494501</v>
+        <v>494524</v>
       </c>
       <c r="R22" t="n">
-        <v>7006553</v>
+        <v>7006571</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3457,6 +3436,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3508,10 +3492,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122364212</v>
+        <v>122359111</v>
       </c>
       <c r="B23" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3524,16 +3508,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3542,8 +3526,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -3556,17 +3538,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494582</v>
+        <v>494496</v>
       </c>
       <c r="R23" t="n">
-        <v>7006726</v>
+        <v>7006482</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3600,7 +3582,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3617,29 +3599,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3657,10 +3634,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122355606</v>
+        <v>122360490</v>
       </c>
       <c r="B24" t="n">
-        <v>57390</v>
+        <v>79756</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3669,51 +3646,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494524</v>
+        <v>494402</v>
       </c>
       <c r="R24" t="n">
-        <v>7006571</v>
+        <v>7006360</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3745,11 +3717,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3766,22 +3733,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3799,10 +3766,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122361037</v>
+        <v>122364729</v>
       </c>
       <c r="B25" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3815,37 +3782,49 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494456</v>
+        <v>494499</v>
       </c>
       <c r="R25" t="n">
-        <v>7006360</v>
+        <v>7006492</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3877,6 +3856,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3891,6 +3875,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3903,12 +3892,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3926,10 +3915,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122359011</v>
+        <v>122361119</v>
       </c>
       <c r="B26" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3942,37 +3931,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494502</v>
+        <v>494460</v>
       </c>
       <c r="R26" t="n">
-        <v>7006489</v>
+        <v>7006357</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4004,6 +3998,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4020,22 +4019,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4053,10 +4052,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122360113</v>
+        <v>122361005</v>
       </c>
       <c r="B27" t="n">
-        <v>79756</v>
+        <v>78646</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4065,46 +4064,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494392</v>
+        <v>494444</v>
       </c>
       <c r="R27" t="n">
-        <v>7006448</v>
+        <v>7006335</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4152,22 +4146,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4185,10 +4179,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122355645</v>
+        <v>122355933</v>
       </c>
       <c r="B28" t="n">
-        <v>57527</v>
+        <v>78646</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4201,51 +4195,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494521</v>
+        <v>494462</v>
       </c>
       <c r="R28" t="n">
-        <v>7006584</v>
+        <v>7006583</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4289,6 +4269,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122407942</v>
+        <v>122406983</v>
       </c>
       <c r="B29" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4322,44 +4322,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494566</v>
+        <v>494621</v>
       </c>
       <c r="R29" t="n">
-        <v>7006630</v>
+        <v>7006636</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4394,11 +4384,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4415,22 +4400,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4448,10 +4433,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122407975</v>
+        <v>122408149</v>
       </c>
       <c r="B30" t="n">
-        <v>78646</v>
+        <v>90807</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4464,34 +4449,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494572</v>
+        <v>494574</v>
       </c>
       <c r="R30" t="n">
-        <v>7006632</v>
+        <v>7006638</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4526,6 +4516,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4552,12 +4547,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4575,10 +4570,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406373</v>
+        <v>122407671</v>
       </c>
       <c r="B31" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4591,34 +4586,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494674</v>
+        <v>494534</v>
       </c>
       <c r="R31" t="n">
-        <v>7006716</v>
+        <v>7006518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4653,6 +4658,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov granstam.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4679,12 +4689,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4702,7 +4712,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122406983</v>
+        <v>122407975</v>
       </c>
       <c r="B32" t="n">
         <v>78646</v>
@@ -4742,10 +4752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494621</v>
+        <v>494572</v>
       </c>
       <c r="R32" t="n">
-        <v>7006636</v>
+        <v>7006632</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4829,7 +4839,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122405719</v>
+        <v>122406373</v>
       </c>
       <c r="B33" t="n">
         <v>78646</v>
@@ -4869,10 +4879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494740</v>
+        <v>494674</v>
       </c>
       <c r="R33" t="n">
-        <v>7006719</v>
+        <v>7006716</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4933,12 +4943,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4956,7 +4966,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122406150</v>
+        <v>122406516</v>
       </c>
       <c r="B34" t="n">
         <v>78646</v>
@@ -4996,10 +5006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494722</v>
+        <v>494604</v>
       </c>
       <c r="R34" t="n">
-        <v>7006694</v>
+        <v>7006665</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5083,7 +5093,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122406516</v>
+        <v>122406150</v>
       </c>
       <c r="B35" t="n">
         <v>78646</v>
@@ -5123,10 +5133,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494604</v>
+        <v>494722</v>
       </c>
       <c r="R35" t="n">
-        <v>7006665</v>
+        <v>7006694</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5210,10 +5220,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122407432</v>
+        <v>122405719</v>
       </c>
       <c r="B36" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5226,44 +5236,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494548</v>
+        <v>494740</v>
       </c>
       <c r="R36" t="n">
-        <v>7006529</v>
+        <v>7006719</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5298,11 +5298,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5329,12 +5324,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5352,10 +5347,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122408149</v>
+        <v>122407432</v>
       </c>
       <c r="B37" t="n">
-        <v>90807</v>
+        <v>57374</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5368,39 +5363,44 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494574</v>
+        <v>494548</v>
       </c>
       <c r="R37" t="n">
-        <v>7006638</v>
+        <v>7006529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122407671</v>
+        <v>122407942</v>
       </c>
       <c r="B38" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5505,16 +5505,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494534</v>
+        <v>494566</v>
       </c>
       <c r="R38" t="n">
-        <v>7006518</v>
+        <v>7006630</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5598,22 +5598,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360161</v>
+        <v>122357683</v>
       </c>
       <c r="B2" t="n">
-        <v>79727</v>
+        <v>90819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494380</v>
+        <v>494501</v>
       </c>
       <c r="R2" t="n">
-        <v>7006419</v>
+        <v>7006553</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,11 +758,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,22 +774,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122357683</v>
+        <v>122361119</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
+        <v>79732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,27 +823,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494501</v>
+        <v>494460</v>
       </c>
       <c r="R3" t="n">
-        <v>7006553</v>
+        <v>7006357</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,6 +890,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,22 +911,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360599</v>
+        <v>122359691</v>
       </c>
       <c r="B4" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +960,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494411</v>
+        <v>494410</v>
       </c>
       <c r="R4" t="n">
-        <v>7006366</v>
+        <v>7006434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,11 +1022,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1038,22 +1038,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122357863</v>
+        <v>122360490</v>
       </c>
       <c r="B5" t="n">
-        <v>57527</v>
+        <v>79761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,40 +1083,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1125,13 +1116,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494497</v>
+        <v>494402</v>
       </c>
       <c r="R5" t="n">
-        <v>7006523</v>
+        <v>7006360</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1175,6 +1166,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1192,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122355645</v>
+        <v>122359011</v>
       </c>
       <c r="B6" t="n">
-        <v>57527</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,48 +1219,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494521</v>
+        <v>494502</v>
       </c>
       <c r="R6" t="n">
-        <v>7006584</v>
+        <v>7006489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1296,6 +1293,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1313,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122360218</v>
+        <v>122355933</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,13 +1370,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494394</v>
+        <v>494462</v>
       </c>
       <c r="R7" t="n">
-        <v>7006412</v>
+        <v>7006583</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1440,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122364318</v>
+        <v>122360500</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>79768</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,49 +1469,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494511</v>
+        <v>494402</v>
       </c>
       <c r="R8" t="n">
-        <v>7006626</v>
+        <v>7006360</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1526,11 +1540,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1545,29 +1554,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1585,10 +1589,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122364537</v>
+        <v>122361274</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1601,49 +1605,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494454</v>
+        <v>494472</v>
       </c>
       <c r="R9" t="n">
-        <v>7006579</v>
+        <v>7006382</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1677,7 +1669,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,11 +1686,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1711,12 +1698,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1734,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122361037</v>
+        <v>122364318</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1750,37 +1737,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494456</v>
+        <v>494511</v>
       </c>
       <c r="R10" t="n">
-        <v>7006360</v>
+        <v>7006626</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1812,6 +1807,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1826,6 +1826,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1838,12 +1843,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1861,10 +1866,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122361219</v>
+        <v>122359111</v>
       </c>
       <c r="B11" t="n">
-        <v>79728</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1877,27 +1882,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1906,13 +1916,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494464</v>
+        <v>494496</v>
       </c>
       <c r="R11" t="n">
-        <v>7006354</v>
+        <v>7006482</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1946,7 +1956,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1965,22 +1975,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1998,10 +2008,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122359691</v>
+        <v>122355822</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2014,37 +2024,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494410</v>
+        <v>494487</v>
       </c>
       <c r="R12" t="n">
-        <v>7006434</v>
+        <v>7006560</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2076,6 +2096,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2102,12 +2127,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2125,10 +2150,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122354497</v>
+        <v>122361219</v>
       </c>
       <c r="B13" t="n">
-        <v>57390</v>
+        <v>79733</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2141,44 +2166,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494602</v>
+        <v>494464</v>
       </c>
       <c r="R13" t="n">
-        <v>7006702</v>
+        <v>7006354</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2215,7 +2235,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2234,22 +2254,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2267,10 +2287,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122364212</v>
+        <v>122360599</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2283,49 +2303,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494582</v>
+        <v>494411</v>
       </c>
       <c r="R14" t="n">
-        <v>7006726</v>
+        <v>7006366</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2359,7 +2367,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2376,29 +2384,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2416,10 +2419,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122359011</v>
+        <v>122355606</v>
       </c>
       <c r="B15" t="n">
-        <v>78646</v>
+        <v>57395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2432,34 +2435,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494502</v>
+        <v>494524</v>
       </c>
       <c r="R15" t="n">
-        <v>7006489</v>
+        <v>7006571</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2494,6 +2507,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2520,12 +2538,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2543,10 +2561,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122355540</v>
+        <v>122357863</v>
       </c>
       <c r="B16" t="n">
-        <v>78646</v>
+        <v>57532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2559,34 +2577,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494535</v>
+        <v>494497</v>
       </c>
       <c r="R16" t="n">
-        <v>7006574</v>
+        <v>7006523</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2633,26 +2665,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2670,10 +2682,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122360113</v>
+        <v>122360218</v>
       </c>
       <c r="B17" t="n">
-        <v>79756</v>
+        <v>78651</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2682,43 +2694,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494392</v>
+        <v>494394</v>
       </c>
       <c r="R17" t="n">
-        <v>7006448</v>
+        <v>7006412</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2769,22 +2776,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2802,10 +2809,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122361274</v>
+        <v>122364537</v>
       </c>
       <c r="B18" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2818,37 +2825,49 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494472</v>
+        <v>494454</v>
       </c>
       <c r="R18" t="n">
-        <v>7006382</v>
+        <v>7006579</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2882,7 +2901,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2899,6 +2918,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2911,12 +2935,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2934,10 +2958,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122357658</v>
+        <v>122355540</v>
       </c>
       <c r="B19" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2950,44 +2974,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494515</v>
+        <v>494535</v>
       </c>
       <c r="R19" t="n">
-        <v>7006545</v>
+        <v>7006574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3022,11 +3036,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3053,12 +3062,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3076,10 +3085,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122355822</v>
+        <v>122360161</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3092,44 +3101,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494487</v>
+        <v>494380</v>
       </c>
       <c r="R20" t="n">
-        <v>7006560</v>
+        <v>7006419</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3166,7 +3165,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3185,22 +3184,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3218,10 +3217,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122360500</v>
+        <v>122360113</v>
       </c>
       <c r="B21" t="n">
-        <v>79763</v>
+        <v>79761</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3234,21 +3233,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3263,10 +3262,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494402</v>
+        <v>494392</v>
       </c>
       <c r="R21" t="n">
-        <v>7006360</v>
+        <v>7006448</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3350,10 +3349,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122355606</v>
+        <v>122354497</v>
       </c>
       <c r="B22" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3386,7 +3385,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3400,13 +3399,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494524</v>
+        <v>494602</v>
       </c>
       <c r="R22" t="n">
-        <v>7006571</v>
+        <v>7006702</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3440,7 +3439,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3469,12 +3468,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3492,10 +3491,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122359111</v>
+        <v>122364212</v>
       </c>
       <c r="B23" t="n">
-        <v>57390</v>
+        <v>57379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3508,16 +3507,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3526,6 +3525,8 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -3538,17 +3539,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494496</v>
+        <v>494582</v>
       </c>
       <c r="R23" t="n">
-        <v>7006482</v>
+        <v>7006726</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3582,7 +3583,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3599,24 +3600,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3634,10 +3640,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122360490</v>
+        <v>122357658</v>
       </c>
       <c r="B24" t="n">
-        <v>79756</v>
+        <v>57395</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3646,31 +3652,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3679,13 +3690,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494402</v>
+        <v>494515</v>
       </c>
       <c r="R24" t="n">
-        <v>7006360</v>
+        <v>7006545</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3717,6 +3728,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3733,22 +3749,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3769,7 +3785,7 @@
         <v>122364729</v>
       </c>
       <c r="B25" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3915,10 +3931,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122361119</v>
+        <v>122361005</v>
       </c>
       <c r="B26" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3931,42 +3947,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494460</v>
+        <v>494444</v>
       </c>
       <c r="R26" t="n">
-        <v>7006357</v>
+        <v>7006335</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3998,11 +4009,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4019,22 +4025,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4052,10 +4058,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122361005</v>
+        <v>122355645</v>
       </c>
       <c r="B27" t="n">
-        <v>78646</v>
+        <v>57532</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4068,37 +4074,51 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494444</v>
+        <v>494521</v>
       </c>
       <c r="R27" t="n">
-        <v>7006335</v>
+        <v>7006584</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4142,26 +4162,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122355933</v>
+        <v>122361037</v>
       </c>
       <c r="B28" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494462</v>
+        <v>494456</v>
       </c>
       <c r="R28" t="n">
-        <v>7006583</v>
+        <v>7006360</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122406983</v>
+        <v>122407975</v>
       </c>
       <c r="B29" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494621</v>
+        <v>494572</v>
       </c>
       <c r="R29" t="n">
-        <v>7006636</v>
+        <v>7006632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4433,10 +4433,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122408149</v>
+        <v>122407942</v>
       </c>
       <c r="B30" t="n">
-        <v>90807</v>
+        <v>57395</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4449,39 +4449,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494574</v>
+        <v>494566</v>
       </c>
       <c r="R30" t="n">
-        <v>7006638</v>
+        <v>7006630</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4518,7 +4523,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4537,12 +4542,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4552,7 +4557,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4570,10 +4575,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122407671</v>
+        <v>122406150</v>
       </c>
       <c r="B31" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4586,44 +4591,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494534</v>
+        <v>494722</v>
       </c>
       <c r="R31" t="n">
-        <v>7006518</v>
+        <v>7006694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4658,11 +4653,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4689,12 +4679,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4712,10 +4702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122407975</v>
+        <v>122407432</v>
       </c>
       <c r="B32" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4728,34 +4718,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494572</v>
+        <v>494548</v>
       </c>
       <c r="R32" t="n">
-        <v>7006632</v>
+        <v>7006529</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4790,6 +4790,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4816,12 +4821,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4839,10 +4844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122406373</v>
+        <v>122408149</v>
       </c>
       <c r="B33" t="n">
-        <v>78646</v>
+        <v>90819</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4855,34 +4860,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494674</v>
+        <v>494574</v>
       </c>
       <c r="R33" t="n">
-        <v>7006716</v>
+        <v>7006638</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4917,6 +4927,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4943,12 +4958,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4966,10 +4981,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122406516</v>
+        <v>122407671</v>
       </c>
       <c r="B34" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4982,34 +4997,44 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494604</v>
+        <v>494534</v>
       </c>
       <c r="R34" t="n">
-        <v>7006665</v>
+        <v>7006518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5044,6 +5069,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov granstam.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5070,12 +5100,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5093,10 +5123,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122406150</v>
+        <v>122406983</v>
       </c>
       <c r="B35" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5133,10 +5163,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494722</v>
+        <v>494621</v>
       </c>
       <c r="R35" t="n">
-        <v>7006694</v>
+        <v>7006636</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5220,10 +5250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122405719</v>
+        <v>122406373</v>
       </c>
       <c r="B36" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5260,10 +5290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494740</v>
+        <v>494674</v>
       </c>
       <c r="R36" t="n">
-        <v>7006719</v>
+        <v>7006716</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5324,12 +5354,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5347,10 +5377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122407432</v>
+        <v>122405719</v>
       </c>
       <c r="B37" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5363,44 +5393,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494548</v>
+        <v>494740</v>
       </c>
       <c r="R37" t="n">
-        <v>7006529</v>
+        <v>7006719</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5435,11 +5455,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5466,12 +5481,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5489,10 +5504,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122407942</v>
+        <v>122406516</v>
       </c>
       <c r="B38" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5505,44 +5520,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494566</v>
+        <v>494604</v>
       </c>
       <c r="R38" t="n">
-        <v>7006630</v>
+        <v>7006665</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5577,11 +5582,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5598,22 +5598,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122357683</v>
+        <v>122355540</v>
       </c>
       <c r="B2" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494501</v>
+        <v>494535</v>
       </c>
       <c r="R2" t="n">
-        <v>7006553</v>
+        <v>7006574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361119</v>
+        <v>122360490</v>
       </c>
       <c r="B3" t="n">
-        <v>79732</v>
+        <v>79761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,31 +814,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494460</v>
+        <v>494402</v>
       </c>
       <c r="R3" t="n">
-        <v>7006357</v>
+        <v>7006360</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,11 +883,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -944,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122359691</v>
+        <v>122361119</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,37 +950,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494410</v>
+        <v>494460</v>
       </c>
       <c r="R4" t="n">
-        <v>7006434</v>
+        <v>7006357</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,6 +1017,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1038,22 +1038,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360490</v>
+        <v>122364537</v>
       </c>
       <c r="B5" t="n">
-        <v>79761</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,46 +1083,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494402</v>
+        <v>494454</v>
       </c>
       <c r="R5" t="n">
-        <v>7006360</v>
+        <v>7006579</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1154,6 +1161,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1168,24 +1180,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,7 +1220,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359011</v>
+        <v>122361274</v>
       </c>
       <c r="B6" t="n">
         <v>78651</v>
@@ -1243,10 +1260,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494502</v>
+        <v>494472</v>
       </c>
       <c r="R6" t="n">
-        <v>7006489</v>
+        <v>7006382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,6 +1296,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122355933</v>
+        <v>122364318</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,37 +1368,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494462</v>
+        <v>494511</v>
       </c>
       <c r="R7" t="n">
-        <v>7006583</v>
+        <v>7006626</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1408,6 +1438,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1422,6 +1457,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1434,12 +1474,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1457,10 +1497,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122360500</v>
+        <v>122360161</v>
       </c>
       <c r="B8" t="n">
-        <v>79768</v>
+        <v>79732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,46 +1509,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494402</v>
+        <v>494380</v>
       </c>
       <c r="R8" t="n">
-        <v>7006360</v>
+        <v>7006419</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1538,6 +1573,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1589,10 +1629,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361274</v>
+        <v>122357658</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1605,34 +1645,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494472</v>
+        <v>494515</v>
       </c>
       <c r="R9" t="n">
-        <v>7006382</v>
+        <v>7006545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1719,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1698,12 +1748,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1721,10 +1771,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122364318</v>
+        <v>122360218</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1737,45 +1787,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494511</v>
+        <v>494394</v>
       </c>
       <c r="R10" t="n">
-        <v>7006626</v>
+        <v>7006412</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1807,11 +1849,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1826,11 +1863,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1843,12 +1875,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1866,10 +1898,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122359111</v>
+        <v>122364729</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,16 +1914,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1900,6 +1932,8 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1912,17 +1946,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494496</v>
+        <v>494499</v>
       </c>
       <c r="R11" t="n">
-        <v>7006482</v>
+        <v>7006492</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1956,7 +1990,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1973,24 +2007,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2008,7 +2047,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122355822</v>
+        <v>122364212</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -2042,9 +2081,11 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2054,17 +2095,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494487</v>
+        <v>494582</v>
       </c>
       <c r="R12" t="n">
-        <v>7006560</v>
+        <v>7006726</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2098,7 +2139,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,6 +2154,11 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2150,10 +2196,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122361219</v>
+        <v>122354497</v>
       </c>
       <c r="B13" t="n">
-        <v>79733</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2166,39 +2212,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494464</v>
+        <v>494602</v>
       </c>
       <c r="R13" t="n">
-        <v>7006354</v>
+        <v>7006702</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2235,7 +2286,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2254,22 +2305,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2287,10 +2338,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122360599</v>
+        <v>122359691</v>
       </c>
       <c r="B14" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2303,21 +2354,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2327,10 +2378,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494411</v>
+        <v>494410</v>
       </c>
       <c r="R14" t="n">
-        <v>7006366</v>
+        <v>7006434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2365,11 +2416,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2386,22 +2432,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2419,10 +2465,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122355606</v>
+        <v>122360113</v>
       </c>
       <c r="B15" t="n">
-        <v>57395</v>
+        <v>79761</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2431,48 +2477,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494524</v>
+        <v>494392</v>
       </c>
       <c r="R15" t="n">
-        <v>7006571</v>
+        <v>7006448</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2507,11 +2548,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2528,22 +2564,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2561,10 +2597,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357863</v>
+        <v>122355933</v>
       </c>
       <c r="B16" t="n">
-        <v>57532</v>
+        <v>78651</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2577,51 +2613,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494497</v>
+        <v>494462</v>
       </c>
       <c r="R16" t="n">
-        <v>7006523</v>
+        <v>7006583</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2665,6 +2687,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2682,10 +2724,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122360218</v>
+        <v>122361219</v>
       </c>
       <c r="B17" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2698,37 +2740,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494394</v>
+        <v>494464</v>
       </c>
       <c r="R17" t="n">
-        <v>7006412</v>
+        <v>7006354</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2760,6 +2807,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2776,22 +2828,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2809,10 +2861,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122364537</v>
+        <v>122359011</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2825,49 +2877,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494454</v>
+        <v>494502</v>
       </c>
       <c r="R18" t="n">
-        <v>7006579</v>
+        <v>7006489</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2899,11 +2939,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2918,11 +2953,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2935,12 +2965,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2958,10 +2988,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122355540</v>
+        <v>122355822</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2974,37 +3004,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494535</v>
+        <v>494487</v>
       </c>
       <c r="R19" t="n">
-        <v>7006574</v>
+        <v>7006560</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3036,6 +3076,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3062,12 +3107,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3085,10 +3130,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122360161</v>
+        <v>122361005</v>
       </c>
       <c r="B20" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3101,21 +3146,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3125,10 +3170,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494380</v>
+        <v>494444</v>
       </c>
       <c r="R20" t="n">
-        <v>7006419</v>
+        <v>7006335</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3163,11 +3208,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3184,22 +3224,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3217,10 +3257,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122360113</v>
+        <v>122357683</v>
       </c>
       <c r="B21" t="n">
-        <v>79761</v>
+        <v>90826</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3229,31 +3269,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3262,10 +3302,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494392</v>
+        <v>494501</v>
       </c>
       <c r="R21" t="n">
-        <v>7006448</v>
+        <v>7006553</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3316,22 +3356,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3349,10 +3389,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122354497</v>
+        <v>122360500</v>
       </c>
       <c r="B22" t="n">
-        <v>57395</v>
+        <v>79768</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3361,51 +3401,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494602</v>
+        <v>494402</v>
       </c>
       <c r="R22" t="n">
-        <v>7006702</v>
+        <v>7006360</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3437,11 +3472,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3458,22 +3488,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3491,10 +3521,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122364212</v>
+        <v>122355645</v>
       </c>
       <c r="B23" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3507,29 +3537,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3539,17 +3571,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494582</v>
+        <v>494521</v>
       </c>
       <c r="R23" t="n">
-        <v>7006726</v>
+        <v>7006584</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3581,11 +3613,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3598,31 +3625,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3640,10 +3642,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122357658</v>
+        <v>122361037</v>
       </c>
       <c r="B24" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3656,47 +3658,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494515</v>
+        <v>494456</v>
       </c>
       <c r="R24" t="n">
-        <v>7006545</v>
+        <v>7006360</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3728,11 +3720,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3759,12 +3746,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3782,10 +3769,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122364729</v>
+        <v>122359111</v>
       </c>
       <c r="B25" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3798,16 +3785,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3816,8 +3803,6 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -3830,17 +3815,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494499</v>
+        <v>494496</v>
       </c>
       <c r="R25" t="n">
-        <v>7006492</v>
+        <v>7006482</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3874,7 +3859,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3891,29 +3876,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3931,10 +3911,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122361005</v>
+        <v>122357863</v>
       </c>
       <c r="B26" t="n">
-        <v>78651</v>
+        <v>57532</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3947,37 +3927,51 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494444</v>
+        <v>494497</v>
       </c>
       <c r="R26" t="n">
-        <v>7006335</v>
+        <v>7006523</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4021,26 +4015,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4058,10 +4032,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122355645</v>
+        <v>122360599</v>
       </c>
       <c r="B27" t="n">
-        <v>57532</v>
+        <v>79732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4074,48 +4048,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494521</v>
+        <v>494411</v>
       </c>
       <c r="R27" t="n">
-        <v>7006584</v>
+        <v>7006366</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4150,6 +4110,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4162,6 +4127,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4179,10 +4164,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122361037</v>
+        <v>122355606</v>
       </c>
       <c r="B28" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4195,37 +4180,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494456</v>
+        <v>494524</v>
       </c>
       <c r="R28" t="n">
-        <v>7006360</v>
+        <v>7006571</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4257,6 +4252,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122407975</v>
+        <v>122408149</v>
       </c>
       <c r="B29" t="n">
-        <v>78651</v>
+        <v>90826</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4322,34 +4322,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494572</v>
+        <v>494574</v>
       </c>
       <c r="R29" t="n">
-        <v>7006632</v>
+        <v>7006638</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4384,6 +4389,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4410,12 +4420,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4433,10 +4443,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122407942</v>
+        <v>122406983</v>
       </c>
       <c r="B30" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4449,44 +4459,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494566</v>
+        <v>494621</v>
       </c>
       <c r="R30" t="n">
-        <v>7006630</v>
+        <v>7006636</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4521,11 +4521,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4542,22 +4537,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4575,7 +4570,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406150</v>
+        <v>122406516</v>
       </c>
       <c r="B31" t="n">
         <v>78651</v>
@@ -4615,10 +4610,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494722</v>
+        <v>494604</v>
       </c>
       <c r="R31" t="n">
-        <v>7006694</v>
+        <v>7006665</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4702,10 +4697,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122407432</v>
+        <v>122405719</v>
       </c>
       <c r="B32" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4718,44 +4713,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494548</v>
+        <v>494740</v>
       </c>
       <c r="R32" t="n">
-        <v>7006529</v>
+        <v>7006719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4790,11 +4775,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4821,12 +4801,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4844,10 +4824,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122408149</v>
+        <v>122406150</v>
       </c>
       <c r="B33" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4860,39 +4840,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494574</v>
+        <v>494722</v>
       </c>
       <c r="R33" t="n">
-        <v>7006638</v>
+        <v>7006694</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4927,11 +4902,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4958,12 +4928,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4981,10 +4951,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122407671</v>
+        <v>122407975</v>
       </c>
       <c r="B34" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4997,44 +4967,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494534</v>
+        <v>494572</v>
       </c>
       <c r="R34" t="n">
-        <v>7006518</v>
+        <v>7006632</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5069,11 +5029,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5100,12 +5055,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5123,7 +5078,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122406983</v>
+        <v>122406373</v>
       </c>
       <c r="B35" t="n">
         <v>78651</v>
@@ -5163,10 +5118,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494621</v>
+        <v>494674</v>
       </c>
       <c r="R35" t="n">
-        <v>7006636</v>
+        <v>7006716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5227,12 +5182,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5250,10 +5205,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122406373</v>
+        <v>122407942</v>
       </c>
       <c r="B36" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5266,34 +5221,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494674</v>
+        <v>494566</v>
       </c>
       <c r="R36" t="n">
-        <v>7006716</v>
+        <v>7006630</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5328,6 +5293,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5344,22 +5314,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5377,10 +5347,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122405719</v>
+        <v>122407432</v>
       </c>
       <c r="B37" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5393,34 +5363,44 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494740</v>
+        <v>494548</v>
       </c>
       <c r="R37" t="n">
-        <v>7006719</v>
+        <v>7006529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5455,6 +5435,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5481,12 +5466,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5504,10 +5489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122406516</v>
+        <v>122407671</v>
       </c>
       <c r="B38" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5520,34 +5505,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494604</v>
+        <v>494534</v>
       </c>
       <c r="R38" t="n">
-        <v>7006665</v>
+        <v>7006518</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5582,6 +5577,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov granstam.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -2988,10 +2988,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122355822</v>
+        <v>122361005</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3004,44 +3004,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494487</v>
+        <v>494444</v>
       </c>
       <c r="R19" t="n">
-        <v>7006560</v>
+        <v>7006335</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -3076,11 +3066,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3107,12 +3092,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3130,10 +3115,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122361005</v>
+        <v>122355822</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3146,34 +3131,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494444</v>
+        <v>494487</v>
       </c>
       <c r="R20" t="n">
-        <v>7006335</v>
+        <v>7006560</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3208,6 +3203,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122361037</v>
+        <v>122357863</v>
       </c>
       <c r="B24" t="n">
-        <v>78651</v>
+        <v>57532</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3658,37 +3658,51 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494456</v>
+        <v>494497</v>
       </c>
       <c r="R24" t="n">
-        <v>7006360</v>
+        <v>7006523</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3732,26 +3746,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3769,10 +3763,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122359111</v>
+        <v>122361037</v>
       </c>
       <c r="B25" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3785,47 +3779,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494496</v>
+        <v>494456</v>
       </c>
       <c r="R25" t="n">
-        <v>7006482</v>
+        <v>7006360</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3857,11 +3841,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3878,22 +3857,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3911,10 +3890,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122357863</v>
+        <v>122359111</v>
       </c>
       <c r="B26" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3927,31 +3906,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3965,13 +3940,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494497</v>
+        <v>494496</v>
       </c>
       <c r="R26" t="n">
-        <v>7006523</v>
+        <v>7006482</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4003,6 +3978,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4015,6 +3995,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122364537</v>
+        <v>122361274</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,49 +1087,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494454</v>
+        <v>494472</v>
       </c>
       <c r="R5" t="n">
-        <v>7006579</v>
+        <v>7006382</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1163,7 +1151,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,11 +1168,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1197,12 +1180,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1220,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122361274</v>
+        <v>122364537</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1236,37 +1219,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494472</v>
+        <v>494454</v>
       </c>
       <c r="R6" t="n">
-        <v>7006382</v>
+        <v>7006579</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,6 +1312,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122355540</v>
+        <v>122361119</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494535</v>
+        <v>494460</v>
       </c>
       <c r="R2" t="n">
-        <v>7006574</v>
+        <v>7006357</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +753,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -767,24 +772,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360490</v>
+        <v>122355606</v>
       </c>
       <c r="B3" t="n">
-        <v>79761</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,46 +814,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494402</v>
+        <v>494524</v>
       </c>
       <c r="R3" t="n">
-        <v>7006360</v>
+        <v>7006571</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +885,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -899,24 +904,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361119</v>
+        <v>122361005</v>
       </c>
       <c r="B4" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,42 +950,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494460</v>
+        <v>494444</v>
       </c>
       <c r="R4" t="n">
-        <v>7006357</v>
+        <v>7006335</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,11 +1007,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1036,24 +1021,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122361274</v>
+        <v>122361219</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>79734</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,37 +1067,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494472</v>
+        <v>494464</v>
       </c>
       <c r="R5" t="n">
-        <v>7006382</v>
+        <v>7006354</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1151,7 +1131,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,24 +1148,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1221,11 +1196,6 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1317,11 +1287,6 @@
           <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1352,10 +1317,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122364318</v>
+        <v>122357863</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,45 +1333,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494511</v>
+        <v>494497</v>
       </c>
       <c r="R7" t="n">
-        <v>7006626</v>
+        <v>7006523</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1438,11 +1404,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1455,31 +1416,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1497,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122360161</v>
+        <v>122355645</v>
       </c>
       <c r="B8" t="n">
-        <v>79732</v>
+        <v>57532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1513,37 +1449,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494380</v>
+        <v>494521</v>
       </c>
       <c r="R8" t="n">
-        <v>7006419</v>
+        <v>7006584</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1575,11 +1520,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1592,26 +1532,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1629,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122357658</v>
+        <v>122355822</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1645,16 +1565,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1665,7 +1580,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1679,13 +1594,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494515</v>
+        <v>494487</v>
       </c>
       <c r="R9" t="n">
-        <v>7006545</v>
+        <v>7006560</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1719,7 +1634,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1736,11 +1651,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1748,12 +1658,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1771,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122360218</v>
+        <v>122360490</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>79762</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1783,41 +1693,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494394</v>
+        <v>494402</v>
       </c>
       <c r="R10" t="n">
-        <v>7006412</v>
+        <v>7006360</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1863,24 +1773,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1898,10 +1803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122364729</v>
+        <v>122359111</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1914,16 +1819,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1932,8 +1832,6 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1946,17 +1844,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494499</v>
+        <v>494496</v>
       </c>
       <c r="R11" t="n">
-        <v>7006492</v>
+        <v>7006482</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1990,7 +1888,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2007,29 +1905,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2047,10 +1935,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122364212</v>
+        <v>122359691</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2063,49 +1951,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494582</v>
+        <v>494410</v>
       </c>
       <c r="R12" t="n">
-        <v>7006726</v>
+        <v>7006434</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2137,11 +2008,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2156,16 +2022,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2173,12 +2029,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2196,10 +2052,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122354497</v>
+        <v>122355933</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2212,44 +2068,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494602</v>
+        <v>494462</v>
       </c>
       <c r="R13" t="n">
-        <v>7006702</v>
+        <v>7006583</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2284,11 +2125,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2303,11 +2139,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK13" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2315,12 +2146,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2338,10 +2169,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122359691</v>
+        <v>122357683</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2354,34 +2185,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494410</v>
+        <v>494501</v>
       </c>
       <c r="R14" t="n">
-        <v>7006434</v>
+        <v>7006553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2430,11 +2261,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK14" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2442,12 +2268,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2465,10 +2291,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122360113</v>
+        <v>122360500</v>
       </c>
       <c r="B15" t="n">
-        <v>79761</v>
+        <v>79769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2481,21 +2307,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>6464</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2510,10 +2331,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494392</v>
+        <v>494402</v>
       </c>
       <c r="R15" t="n">
-        <v>7006448</v>
+        <v>7006360</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2560,11 +2381,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2597,10 +2413,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122355933</v>
+        <v>122361037</v>
       </c>
       <c r="B16" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2615,11 +2431,6 @@
       <c r="E16" t="n">
         <v>6425</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2637,10 +2448,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494462</v>
+        <v>494456</v>
       </c>
       <c r="R16" t="n">
-        <v>7006583</v>
+        <v>7006360</v>
       </c>
       <c r="S16" t="n">
         <v>7</v>
@@ -2689,11 +2500,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2701,12 +2507,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2724,10 +2530,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122361219</v>
+        <v>122364212</v>
       </c>
       <c r="B17" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2740,42 +2546,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494464</v>
+        <v>494582</v>
       </c>
       <c r="R17" t="n">
-        <v>7006354</v>
+        <v>7006726</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2809,7 +2617,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2826,24 +2634,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2864,7 +2672,7 @@
         <v>122359011</v>
       </c>
       <c r="B18" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2879,11 +2687,6 @@
       <c r="E18" t="n">
         <v>6425</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2951,11 +2754,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -2988,10 +2786,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122361005</v>
+        <v>122360218</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3006,11 +2804,6 @@
       <c r="E19" t="n">
         <v>6425</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3028,13 +2821,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494444</v>
+        <v>494394</v>
       </c>
       <c r="R19" t="n">
-        <v>7006335</v>
+        <v>7006412</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3078,11 +2871,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3115,10 +2903,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122355822</v>
+        <v>122357658</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3131,16 +2919,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3151,7 +2934,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3165,13 +2948,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494487</v>
+        <v>494515</v>
       </c>
       <c r="R20" t="n">
-        <v>7006560</v>
+        <v>7006545</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3205,7 +2988,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3222,11 +3005,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK20" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3234,12 +3012,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3257,10 +3035,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122357683</v>
+        <v>122354497</v>
       </c>
       <c r="B21" t="n">
-        <v>90826</v>
+        <v>57395</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3273,42 +3051,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494501</v>
+        <v>494602</v>
       </c>
       <c r="R21" t="n">
-        <v>7006553</v>
+        <v>7006702</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3340,6 +3118,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3354,11 +3137,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK21" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3366,12 +3144,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3389,10 +3167,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122360500</v>
+        <v>122360113</v>
       </c>
       <c r="B22" t="n">
-        <v>79768</v>
+        <v>79762</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3405,21 +3183,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3434,10 +3207,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494402</v>
+        <v>494392</v>
       </c>
       <c r="R22" t="n">
-        <v>7006360</v>
+        <v>7006448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3484,11 +3257,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3521,10 +3289,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122355645</v>
+        <v>122355540</v>
       </c>
       <c r="B23" t="n">
-        <v>57532</v>
+        <v>78652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3537,48 +3305,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494521</v>
+        <v>494535</v>
       </c>
       <c r="R23" t="n">
-        <v>7006584</v>
+        <v>7006574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3625,6 +3374,21 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3642,10 +3406,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122357863</v>
+        <v>122360599</v>
       </c>
       <c r="B24" t="n">
-        <v>57532</v>
+        <v>79733</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3658,48 +3422,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494497</v>
+        <v>494411</v>
       </c>
       <c r="R24" t="n">
-        <v>7006523</v>
+        <v>7006366</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3734,6 +3479,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3746,6 +3496,21 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3763,10 +3528,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122361037</v>
+        <v>122361274</v>
       </c>
       <c r="B25" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3781,11 +3546,6 @@
       <c r="E25" t="n">
         <v>6425</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3803,13 +3563,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494456</v>
+        <v>494472</v>
       </c>
       <c r="R25" t="n">
-        <v>7006360</v>
+        <v>7006382</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3841,6 +3601,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3855,11 +3620,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK25" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3867,12 +3627,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3890,10 +3650,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122359111</v>
+        <v>122360161</v>
       </c>
       <c r="B26" t="n">
-        <v>57395</v>
+        <v>79733</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3906,44 +3666,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494496</v>
+        <v>494380</v>
       </c>
       <c r="R26" t="n">
-        <v>7006482</v>
+        <v>7006419</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3980,7 +3725,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3997,24 +3742,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4032,10 +3772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122360599</v>
+        <v>122364318</v>
       </c>
       <c r="B27" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4048,37 +3788,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494411</v>
+        <v>494511</v>
       </c>
       <c r="R27" t="n">
-        <v>7006366</v>
+        <v>7006626</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4112,7 +3855,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4129,24 +3872,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4164,10 +3907,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122355606</v>
+        <v>122364729</v>
       </c>
       <c r="B28" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4180,16 +3923,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4198,6 +3936,8 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4210,17 +3950,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494524</v>
+        <v>494499</v>
       </c>
       <c r="R28" t="n">
-        <v>7006571</v>
+        <v>7006492</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4254,7 +3994,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4271,9 +4011,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -4283,12 +4023,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,10 +4046,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122408149</v>
+        <v>122406516</v>
       </c>
       <c r="B29" t="n">
-        <v>90826</v>
+        <v>78652</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4322,39 +4062,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494574</v>
+        <v>494604</v>
       </c>
       <c r="R29" t="n">
-        <v>7006638</v>
+        <v>7006665</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4389,11 +4119,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4408,11 +4133,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4420,12 +4140,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4443,10 +4163,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122406983</v>
+        <v>122406373</v>
       </c>
       <c r="B30" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4461,11 +4181,6 @@
       <c r="E30" t="n">
         <v>6425</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4483,10 +4198,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494621</v>
+        <v>494674</v>
       </c>
       <c r="R30" t="n">
-        <v>7006636</v>
+        <v>7006716</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4535,11 +4250,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK30" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4547,12 +4257,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4570,10 +4280,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406516</v>
+        <v>122406150</v>
       </c>
       <c r="B31" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4588,11 +4298,6 @@
       <c r="E31" t="n">
         <v>6425</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4610,10 +4315,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494604</v>
+        <v>494722</v>
       </c>
       <c r="R31" t="n">
-        <v>7006665</v>
+        <v>7006694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4660,11 +4365,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -4700,7 +4400,7 @@
         <v>122405719</v>
       </c>
       <c r="B32" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4715,11 +4415,6 @@
       <c r="E32" t="n">
         <v>6425</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4787,11 +4482,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -4824,10 +4514,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122406150</v>
+        <v>122407942</v>
       </c>
       <c r="B33" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4840,34 +4530,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494722</v>
+        <v>494566</v>
       </c>
       <c r="R33" t="n">
-        <v>7006694</v>
+        <v>7006630</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4902,6 +4597,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4916,24 +4616,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4951,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122407975</v>
+        <v>122408149</v>
       </c>
       <c r="B34" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4967,34 +4662,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494572</v>
+        <v>494574</v>
       </c>
       <c r="R34" t="n">
-        <v>7006632</v>
+        <v>7006638</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5029,6 +4724,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5043,11 +4743,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK34" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5055,12 +4750,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5078,10 +4773,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122406373</v>
+        <v>122407432</v>
       </c>
       <c r="B35" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5094,34 +4789,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494674</v>
+        <v>494548</v>
       </c>
       <c r="R35" t="n">
-        <v>7006716</v>
+        <v>7006529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5156,6 +4856,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5170,11 +4875,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK35" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5182,12 +4882,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5205,10 +4905,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122407942</v>
+        <v>122407975</v>
       </c>
       <c r="B36" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5221,44 +4921,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494566</v>
+        <v>494572</v>
       </c>
       <c r="R36" t="n">
-        <v>7006630</v>
+        <v>7006632</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5293,11 +4978,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5312,24 +4992,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5347,7 +5022,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122407432</v>
+        <v>122407671</v>
       </c>
       <c r="B37" t="n">
         <v>57379</v>
@@ -5365,11 +5040,6 @@
       <c r="E37" t="n">
         <v>100109</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5383,7 +5053,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5397,10 +5067,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494548</v>
+        <v>494534</v>
       </c>
       <c r="R37" t="n">
-        <v>7006529</v>
+        <v>7006518</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5437,7 +5107,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska ringhack på en relativt grov granstam.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5452,11 +5122,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -5489,10 +5154,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122407671</v>
+        <v>122406983</v>
       </c>
       <c r="B38" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5505,44 +5170,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494534</v>
+        <v>494621</v>
       </c>
       <c r="R38" t="n">
-        <v>7006518</v>
+        <v>7006636</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5577,11 +5227,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5596,11 +5241,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK38" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5608,12 +5248,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -3167,10 +3167,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122360113</v>
+        <v>122361274</v>
       </c>
       <c r="B22" t="n">
-        <v>79762</v>
+        <v>78652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,38 +3179,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494392</v>
+        <v>494472</v>
       </c>
       <c r="R22" t="n">
-        <v>7006448</v>
+        <v>7006382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,6 +3240,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3261,17 +3261,17 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3289,10 +3289,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122355540</v>
+        <v>122360113</v>
       </c>
       <c r="B23" t="n">
-        <v>78652</v>
+        <v>79762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3301,33 +3301,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494535</v>
+        <v>494392</v>
       </c>
       <c r="R23" t="n">
-        <v>7006574</v>
+        <v>7006448</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3378,17 +3383,17 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3406,10 +3411,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122360599</v>
+        <v>122355540</v>
       </c>
       <c r="B24" t="n">
-        <v>79733</v>
+        <v>78652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3422,29 +3427,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494411</v>
+        <v>494535</v>
       </c>
       <c r="R24" t="n">
-        <v>7006366</v>
+        <v>7006574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3479,11 +3484,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3500,17 +3500,17 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122361274</v>
+        <v>122360599</v>
       </c>
       <c r="B25" t="n">
-        <v>78652</v>
+        <v>79733</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3544,16 +3544,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494472</v>
+        <v>494411</v>
       </c>
       <c r="R25" t="n">
-        <v>7006382</v>
+        <v>7006366</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122408149</v>
+        <v>122407432</v>
       </c>
       <c r="B34" t="n">
-        <v>90831</v>
+        <v>57379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4662,34 +4662,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494574</v>
+        <v>494548</v>
       </c>
       <c r="R34" t="n">
-        <v>7006638</v>
+        <v>7006529</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4726,7 +4731,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4750,12 +4755,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4773,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407432</v>
+        <v>122408149</v>
       </c>
       <c r="B35" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4789,39 +4794,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494548</v>
+        <v>494574</v>
       </c>
       <c r="R35" t="n">
-        <v>7006529</v>
+        <v>7006638</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Gott om fruktkroppar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -4646,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122407432</v>
+        <v>122408149</v>
       </c>
       <c r="B34" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4662,39 +4662,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494548</v>
+        <v>494574</v>
       </c>
       <c r="R34" t="n">
-        <v>7006529</v>
+        <v>7006638</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4731,7 +4726,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Gott om fruktkroppar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4755,12 +4750,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4778,10 +4773,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122408149</v>
+        <v>122407432</v>
       </c>
       <c r="B35" t="n">
-        <v>90831</v>
+        <v>57379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4794,34 +4789,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494574</v>
+        <v>494548</v>
       </c>
       <c r="R35" t="n">
-        <v>7006638</v>
+        <v>7006529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361119</v>
+        <v>122357863</v>
       </c>
       <c r="B2" t="n">
-        <v>79733</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,22 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>103021</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494460</v>
+        <v>494497</v>
       </c>
       <c r="R2" t="n">
-        <v>7006357</v>
+        <v>7006523</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,11 +767,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,21 +779,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122355606</v>
+        <v>122360500</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>79773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,43 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6464</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494524</v>
+        <v>494402</v>
       </c>
       <c r="R3" t="n">
-        <v>7006571</v>
+        <v>7006360</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,11 +879,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -904,19 +893,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361005</v>
+        <v>122361274</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,6 +946,11 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -969,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494444</v>
+        <v>494472</v>
       </c>
       <c r="R4" t="n">
-        <v>7006335</v>
+        <v>7006382</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,6 +1006,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,6 +1023,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1051,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122361219</v>
+        <v>122364318</v>
       </c>
       <c r="B5" t="n">
-        <v>79734</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,37 +1076,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494464</v>
+        <v>494511</v>
       </c>
       <c r="R5" t="n">
-        <v>7006354</v>
+        <v>7006626</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,7 +1148,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,19 +1165,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122364537</v>
+        <v>122360113</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>79766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,48 +1217,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494454</v>
+        <v>494392</v>
       </c>
       <c r="R6" t="n">
-        <v>7006579</v>
+        <v>7006448</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,11 +1288,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1282,24 +1302,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357863</v>
+        <v>122354497</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1333,26 +1353,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1362,17 +1383,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494497</v>
+        <v>494602</v>
       </c>
       <c r="R7" t="n">
-        <v>7006523</v>
+        <v>7006702</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,6 +1425,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1416,6 +1442,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1433,10 +1479,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122355645</v>
+        <v>122361119</v>
       </c>
       <c r="B8" t="n">
-        <v>57532</v>
+        <v>79737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,46 +1495,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494521</v>
+        <v>494460</v>
       </c>
       <c r="R8" t="n">
-        <v>7006584</v>
+        <v>7006357</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1520,6 +1562,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1532,6 +1579,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1549,10 +1616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122355822</v>
+        <v>122364537</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1567,6 +1634,11 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1578,6 +1650,8 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -1590,17 +1664,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494487</v>
+        <v>494454</v>
       </c>
       <c r="R9" t="n">
-        <v>7006560</v>
+        <v>7006579</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1634,7 +1708,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,6 +1723,16 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1681,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122360490</v>
+        <v>122355822</v>
       </c>
       <c r="B10" t="n">
-        <v>79762</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,26 +1777,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1721,10 +1815,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494402</v>
+        <v>494487</v>
       </c>
       <c r="R10" t="n">
-        <v>7006360</v>
+        <v>7006560</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1759,6 +1853,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1773,19 +1872,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1803,10 +1907,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122359111</v>
+        <v>122355645</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>57536</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1819,22 +1923,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1844,17 +1957,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494496</v>
+        <v>494521</v>
       </c>
       <c r="R11" t="n">
-        <v>7006482</v>
+        <v>7006584</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1886,11 +1999,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1903,21 +2011,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1935,10 +2028,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122359691</v>
+        <v>122355606</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1951,29 +2044,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494410</v>
+        <v>494524</v>
       </c>
       <c r="R12" t="n">
-        <v>7006434</v>
+        <v>7006571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2008,6 +2116,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2022,6 +2135,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2029,12 +2147,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2055,7 +2173,7 @@
         <v>122355933</v>
       </c>
       <c r="B13" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2070,6 +2188,11 @@
       <c r="E13" t="n">
         <v>6425</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2137,6 +2260,11 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2169,10 +2297,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357683</v>
+        <v>122361219</v>
       </c>
       <c r="B14" t="n">
-        <v>90831</v>
+        <v>79738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2185,22 +2313,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>2081</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2209,13 +2342,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494501</v>
+        <v>494464</v>
       </c>
       <c r="R14" t="n">
-        <v>7006553</v>
+        <v>7006354</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2247,6 +2380,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2261,19 +2399,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2291,10 +2434,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122360500</v>
+        <v>122364212</v>
       </c>
       <c r="B15" t="n">
-        <v>79769</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2303,41 +2446,53 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494402</v>
+        <v>494582</v>
       </c>
       <c r="R15" t="n">
-        <v>7006360</v>
+        <v>7006726</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2369,6 +2524,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2383,19 +2543,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2413,10 +2583,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122361037</v>
+        <v>122360161</v>
       </c>
       <c r="B16" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2429,16 +2599,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2448,13 +2623,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494456</v>
+        <v>494380</v>
       </c>
       <c r="R16" t="n">
-        <v>7006360</v>
+        <v>7006419</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2486,6 +2661,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2500,19 +2680,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2530,10 +2715,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122364212</v>
+        <v>122360490</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>79766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2542,48 +2727,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494582</v>
+        <v>494402</v>
       </c>
       <c r="R17" t="n">
-        <v>7006726</v>
+        <v>7006360</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2615,11 +2798,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2634,24 +2812,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2669,10 +2847,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122359011</v>
+        <v>122357683</v>
       </c>
       <c r="B18" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2685,29 +2863,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494502</v>
+        <v>494501</v>
       </c>
       <c r="R18" t="n">
-        <v>7006489</v>
+        <v>7006553</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2756,6 +2944,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK18" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2763,12 +2956,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2786,10 +2979,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122360218</v>
+        <v>122364729</v>
       </c>
       <c r="B19" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2802,32 +2995,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494394</v>
+        <v>494499</v>
       </c>
       <c r="R19" t="n">
-        <v>7006412</v>
+        <v>7006492</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2859,6 +3069,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2873,6 +3088,16 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK19" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2880,12 +3105,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2903,10 +3128,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122357658</v>
+        <v>122359111</v>
       </c>
       <c r="B20" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2921,6 +3146,11 @@
       <c r="E20" t="n">
         <v>100049</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -2948,13 +3178,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494515</v>
+        <v>494496</v>
       </c>
       <c r="R20" t="n">
-        <v>7006545</v>
+        <v>7006482</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2988,7 +3218,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3005,9 +3235,14 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -3017,7 +3252,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3035,10 +3270,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122354497</v>
+        <v>122355540</v>
       </c>
       <c r="B21" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3051,42 +3286,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494602</v>
+        <v>494535</v>
       </c>
       <c r="R21" t="n">
-        <v>7006702</v>
+        <v>7006574</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3118,11 +3348,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3137,6 +3362,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK21" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3144,12 +3374,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3167,10 +3397,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122361274</v>
+        <v>122357658</v>
       </c>
       <c r="B22" t="n">
-        <v>78652</v>
+        <v>57399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3183,29 +3413,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494472</v>
+        <v>494515</v>
       </c>
       <c r="R22" t="n">
-        <v>7006382</v>
+        <v>7006545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3242,7 +3487,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3259,6 +3504,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK22" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3266,12 +3516,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3289,10 +3539,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122360113</v>
+        <v>122360218</v>
       </c>
       <c r="B23" t="n">
-        <v>79762</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3301,38 +3551,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494392</v>
+        <v>494394</v>
       </c>
       <c r="R23" t="n">
-        <v>7006448</v>
+        <v>7006412</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3381,19 +3631,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3411,10 +3666,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122355540</v>
+        <v>122361005</v>
       </c>
       <c r="B24" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3429,6 +3684,11 @@
       <c r="E24" t="n">
         <v>6425</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3442,17 +3702,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494535</v>
+        <v>494444</v>
       </c>
       <c r="R24" t="n">
-        <v>7006574</v>
+        <v>7006335</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3496,6 +3756,11 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -3528,10 +3793,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122360599</v>
+        <v>122361037</v>
       </c>
       <c r="B25" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3544,16 +3809,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3563,13 +3833,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494411</v>
+        <v>494456</v>
       </c>
       <c r="R25" t="n">
-        <v>7006366</v>
+        <v>7006360</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3601,11 +3871,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3620,19 +3885,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3650,10 +3920,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122360161</v>
+        <v>122359691</v>
       </c>
       <c r="B26" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3666,16 +3936,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3685,13 +3960,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494380</v>
+        <v>494410</v>
       </c>
       <c r="R26" t="n">
-        <v>7006419</v>
+        <v>7006434</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3723,11 +3998,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3742,19 +4012,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3772,10 +4047,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122364318</v>
+        <v>122360599</v>
       </c>
       <c r="B27" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3788,40 +4063,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494511</v>
+        <v>494411</v>
       </c>
       <c r="R27" t="n">
-        <v>7006626</v>
+        <v>7006366</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3855,7 +4127,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3872,24 +4144,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3907,10 +4179,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122364729</v>
+        <v>122359011</v>
       </c>
       <c r="B28" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3923,44 +4195,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494499</v>
+        <v>494502</v>
       </c>
       <c r="R28" t="n">
-        <v>7006492</v>
+        <v>7006489</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3992,11 +4257,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4011,9 +4271,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -4023,12 +4283,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4046,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122406516</v>
+        <v>122407975</v>
       </c>
       <c r="B29" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4064,6 +4324,11 @@
       <c r="E29" t="n">
         <v>6425</v>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4081,10 +4346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494604</v>
+        <v>494572</v>
       </c>
       <c r="R29" t="n">
-        <v>7006665</v>
+        <v>7006632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4131,6 +4396,11 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -4163,10 +4433,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122406373</v>
+        <v>122405719</v>
       </c>
       <c r="B30" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4181,6 +4451,11 @@
       <c r="E30" t="n">
         <v>6425</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4198,10 +4473,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494674</v>
+        <v>494740</v>
       </c>
       <c r="R30" t="n">
-        <v>7006716</v>
+        <v>7006719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4250,6 +4525,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK30" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4257,12 +4537,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4280,10 +4560,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406150</v>
+        <v>122406516</v>
       </c>
       <c r="B31" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4298,6 +4578,11 @@
       <c r="E31" t="n">
         <v>6425</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4315,10 +4600,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494722</v>
+        <v>494604</v>
       </c>
       <c r="R31" t="n">
-        <v>7006694</v>
+        <v>7006665</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4365,6 +4650,11 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -4397,10 +4687,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122405719</v>
+        <v>122406150</v>
       </c>
       <c r="B32" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4415,6 +4705,11 @@
       <c r="E32" t="n">
         <v>6425</v>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4432,10 +4727,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494740</v>
+        <v>494722</v>
       </c>
       <c r="R32" t="n">
-        <v>7006719</v>
+        <v>7006694</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,6 +4777,11 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -4514,10 +4814,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122407942</v>
+        <v>122408149</v>
       </c>
       <c r="B33" t="n">
-        <v>57395</v>
+        <v>90844</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4530,39 +4830,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494566</v>
+        <v>494574</v>
       </c>
       <c r="R33" t="n">
-        <v>7006630</v>
+        <v>7006638</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4599,7 +4899,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+          <t>Gott om fruktkroppar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4616,9 +4916,14 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -4628,7 +4933,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4646,10 +4951,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122408149</v>
+        <v>122406983</v>
       </c>
       <c r="B34" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4662,34 +4967,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494574</v>
+        <v>494621</v>
       </c>
       <c r="R34" t="n">
-        <v>7006638</v>
+        <v>7006636</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4724,11 +5029,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4743,6 +5043,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK34" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4750,12 +5055,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4773,10 +5078,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407432</v>
+        <v>122407942</v>
       </c>
       <c r="B35" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4789,11 +5094,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4804,7 +5114,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4814,14 +5124,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494548</v>
+        <v>494566</v>
       </c>
       <c r="R35" t="n">
-        <v>7006529</v>
+        <v>7006630</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4858,7 +5168,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4875,19 +5185,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4905,10 +5220,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122407975</v>
+        <v>122407432</v>
       </c>
       <c r="B36" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4921,29 +5236,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494572</v>
+        <v>494548</v>
       </c>
       <c r="R36" t="n">
-        <v>7006632</v>
+        <v>7006529</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4978,6 +5308,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4992,6 +5327,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK36" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4999,12 +5339,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5025,7 +5365,7 @@
         <v>122407671</v>
       </c>
       <c r="B37" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5040,6 +5380,11 @@
       <c r="E37" t="n">
         <v>100109</v>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5122,6 +5467,11 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -5154,10 +5504,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122406983</v>
+        <v>122406373</v>
       </c>
       <c r="B38" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5172,6 +5522,11 @@
       <c r="E38" t="n">
         <v>6425</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5189,10 +5544,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494621</v>
+        <v>494674</v>
       </c>
       <c r="R38" t="n">
-        <v>7006636</v>
+        <v>7006716</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5241,6 +5596,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK38" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5248,12 +5608,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122357863</v>
+        <v>122355645</v>
       </c>
       <c r="B2" t="n">
         <v>57536</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -725,14 +725,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494497</v>
+        <v>494521</v>
       </c>
       <c r="R2" t="n">
-        <v>7006523</v>
+        <v>7006584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360500</v>
+        <v>122357683</v>
       </c>
       <c r="B3" t="n">
-        <v>79773</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494402</v>
+        <v>494501</v>
       </c>
       <c r="R3" t="n">
-        <v>7006360</v>
+        <v>7006553</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,22 +895,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361274</v>
+        <v>122360218</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494472</v>
+        <v>494394</v>
       </c>
       <c r="R4" t="n">
-        <v>7006382</v>
+        <v>7006412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,11 +1004,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122364318</v>
+        <v>122361119</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,45 +1071,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494511</v>
+        <v>494460</v>
       </c>
       <c r="R5" t="n">
-        <v>7006626</v>
+        <v>7006357</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1148,7 +1140,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,29 +1157,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1205,10 +1192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122360113</v>
+        <v>122354497</v>
       </c>
       <c r="B6" t="n">
-        <v>79766</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,46 +1204,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494392</v>
+        <v>494602</v>
       </c>
       <c r="R6" t="n">
-        <v>7006448</v>
+        <v>7006702</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,6 +1280,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1304,22 +1301,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1337,7 +1334,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122354497</v>
+        <v>122359111</v>
       </c>
       <c r="B7" t="n">
         <v>57399</v>
@@ -1373,7 +1370,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1383,17 +1380,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494602</v>
+        <v>494496</v>
       </c>
       <c r="R7" t="n">
-        <v>7006702</v>
+        <v>7006482</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1427,7 +1424,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,22 +1443,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1479,10 +1476,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122361119</v>
+        <v>122359011</v>
       </c>
       <c r="B8" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1495,42 +1492,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494460</v>
+        <v>494502</v>
       </c>
       <c r="R8" t="n">
-        <v>7006357</v>
+        <v>7006489</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1562,11 +1554,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1583,22 +1570,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1616,10 +1603,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122364537</v>
+        <v>122361274</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,49 +1619,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494454</v>
+        <v>494472</v>
       </c>
       <c r="R9" t="n">
-        <v>7006579</v>
+        <v>7006382</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1708,7 +1683,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1725,11 +1700,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1742,12 +1712,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1765,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122355822</v>
+        <v>122361005</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1781,44 +1751,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494487</v>
+        <v>494444</v>
       </c>
       <c r="R10" t="n">
-        <v>7006560</v>
+        <v>7006335</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1853,11 +1813,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1884,12 +1839,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1907,10 +1862,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122355645</v>
+        <v>122359691</v>
       </c>
       <c r="B11" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1923,48 +1878,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494521</v>
+        <v>494410</v>
       </c>
       <c r="R11" t="n">
-        <v>7006584</v>
+        <v>7006434</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2011,6 +1952,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2028,10 +1989,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122355606</v>
+        <v>122364212</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2044,16 +2005,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2062,6 +2023,8 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2074,17 +2037,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494524</v>
+        <v>494582</v>
       </c>
       <c r="R12" t="n">
-        <v>7006571</v>
+        <v>7006726</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2118,7 +2081,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2135,6 +2098,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2147,12 +2115,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2170,10 +2138,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122355933</v>
+        <v>122355822</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2186,37 +2154,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494462</v>
+        <v>494487</v>
       </c>
       <c r="R13" t="n">
-        <v>7006583</v>
+        <v>7006560</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2248,6 +2226,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2274,12 +2257,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2297,10 +2280,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122361219</v>
+        <v>122361037</v>
       </c>
       <c r="B14" t="n">
-        <v>79738</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2313,39 +2296,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494464</v>
+        <v>494456</v>
       </c>
       <c r="R14" t="n">
-        <v>7006354</v>
+        <v>7006360</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2380,11 +2358,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2401,22 +2374,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2434,10 +2407,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122364212</v>
+        <v>122357658</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2450,16 +2423,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2468,8 +2441,6 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2482,17 +2453,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494582</v>
+        <v>494515</v>
       </c>
       <c r="R15" t="n">
-        <v>7006726</v>
+        <v>7006545</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2526,7 +2497,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2543,11 +2514,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2560,12 +2526,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2583,10 +2549,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122360161</v>
+        <v>122355606</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2599,37 +2565,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494380</v>
+        <v>494524</v>
       </c>
       <c r="R16" t="n">
-        <v>7006419</v>
+        <v>7006571</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2663,7 +2639,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Färska hackspår/födosökspår.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2682,22 +2658,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2715,10 +2691,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122360490</v>
+        <v>122364729</v>
       </c>
       <c r="B17" t="n">
-        <v>79766</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2727,46 +2703,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494402</v>
+        <v>494499</v>
       </c>
       <c r="R17" t="n">
-        <v>7006360</v>
+        <v>7006492</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2798,6 +2781,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2812,24 +2800,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2847,10 +2840,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122357683</v>
+        <v>122360500</v>
       </c>
       <c r="B18" t="n">
-        <v>90844</v>
+        <v>79773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2859,31 +2852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2892,10 +2885,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494501</v>
+        <v>494402</v>
       </c>
       <c r="R18" t="n">
-        <v>7006553</v>
+        <v>7006360</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2946,22 +2939,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2979,10 +2972,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122364729</v>
+        <v>122361219</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2995,49 +2988,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494499</v>
+        <v>494464</v>
       </c>
       <c r="R19" t="n">
-        <v>7006492</v>
+        <v>7006354</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3071,7 +3057,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3088,29 +3074,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3128,10 +3109,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122359111</v>
+        <v>122355540</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3144,47 +3125,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494496</v>
+        <v>494535</v>
       </c>
       <c r="R20" t="n">
-        <v>7006482</v>
+        <v>7006574</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3216,11 +3187,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3237,22 +3203,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3270,10 +3236,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122355540</v>
+        <v>122360490</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>79766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3282,41 +3248,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494535</v>
+        <v>494402</v>
       </c>
       <c r="R21" t="n">
-        <v>7006574</v>
+        <v>7006360</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3364,22 +3335,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3397,10 +3368,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122357658</v>
+        <v>122364537</v>
       </c>
       <c r="B22" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3413,16 +3384,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3431,9 +3402,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3443,17 +3416,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494515</v>
+        <v>494454</v>
       </c>
       <c r="R22" t="n">
-        <v>7006545</v>
+        <v>7006579</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3487,7 +3460,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3504,6 +3477,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3516,12 +3494,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3539,10 +3517,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122360218</v>
+        <v>122360161</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3555,21 +3533,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3579,13 +3557,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494394</v>
+        <v>494380</v>
       </c>
       <c r="R23" t="n">
-        <v>7006412</v>
+        <v>7006419</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3617,6 +3595,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3633,22 +3616,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3666,7 +3649,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122361005</v>
+        <v>122355933</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -3706,13 +3689,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494444</v>
+        <v>494462</v>
       </c>
       <c r="R24" t="n">
-        <v>7006335</v>
+        <v>7006583</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3793,10 +3776,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122361037</v>
+        <v>122360599</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3809,21 +3792,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3833,13 +3816,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494456</v>
+        <v>494411</v>
       </c>
       <c r="R25" t="n">
-        <v>7006360</v>
+        <v>7006366</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3871,6 +3854,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3887,22 +3875,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3920,10 +3908,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122359691</v>
+        <v>122360113</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>79766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3932,38 +3920,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494410</v>
+        <v>494392</v>
       </c>
       <c r="R26" t="n">
-        <v>7006434</v>
+        <v>7006448</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4014,22 +4007,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4047,10 +4040,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122360599</v>
+        <v>122357863</v>
       </c>
       <c r="B27" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4063,34 +4056,48 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494411</v>
+        <v>494497</v>
       </c>
       <c r="R27" t="n">
-        <v>7006366</v>
+        <v>7006523</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4125,11 +4132,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4142,26 +4144,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4179,10 +4161,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122359011</v>
+        <v>122364318</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4195,37 +4177,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494502</v>
+        <v>494511</v>
       </c>
       <c r="R28" t="n">
-        <v>7006489</v>
+        <v>7006626</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4257,6 +4247,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4271,6 +4266,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122407975</v>
+        <v>122407432</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4322,34 +4322,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494572</v>
+        <v>494548</v>
       </c>
       <c r="R29" t="n">
-        <v>7006632</v>
+        <v>7006529</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4384,6 +4394,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4410,12 +4425,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4433,7 +4448,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122405719</v>
+        <v>122407975</v>
       </c>
       <c r="B30" t="n">
         <v>78656</v>
@@ -4473,10 +4488,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494740</v>
+        <v>494572</v>
       </c>
       <c r="R30" t="n">
-        <v>7006719</v>
+        <v>7006632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4687,10 +4702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122406150</v>
+        <v>122407671</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4703,34 +4718,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494722</v>
+        <v>494534</v>
       </c>
       <c r="R32" t="n">
-        <v>7006694</v>
+        <v>7006518</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4765,6 +4790,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov granstam.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4791,12 +4821,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4814,10 +4844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122408149</v>
+        <v>122407942</v>
       </c>
       <c r="B33" t="n">
-        <v>90844</v>
+        <v>57399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4830,39 +4860,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494574</v>
+        <v>494566</v>
       </c>
       <c r="R33" t="n">
-        <v>7006638</v>
+        <v>7006630</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4899,7 +4934,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4918,12 +4953,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -4933,7 +4968,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5078,10 +5113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407942</v>
+        <v>122408149</v>
       </c>
       <c r="B35" t="n">
-        <v>57399</v>
+        <v>90857</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5094,44 +5129,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494566</v>
+        <v>494574</v>
       </c>
       <c r="R35" t="n">
-        <v>7006630</v>
+        <v>7006638</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5168,7 +5198,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+          <t>Gott om fruktkroppar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5187,12 +5217,12 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -5202,7 +5232,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5220,10 +5250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122407432</v>
+        <v>122406373</v>
       </c>
       <c r="B36" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5236,44 +5266,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494548</v>
+        <v>494674</v>
       </c>
       <c r="R36" t="n">
-        <v>7006529</v>
+        <v>7006716</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5308,11 +5328,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5339,12 +5354,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5362,10 +5377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122407671</v>
+        <v>122405719</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5378,44 +5393,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494534</v>
+        <v>494740</v>
       </c>
       <c r="R37" t="n">
-        <v>7006518</v>
+        <v>7006719</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5450,11 +5455,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5481,12 +5481,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5504,7 +5504,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122406373</v>
+        <v>122406150</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494674</v>
+        <v>494722</v>
       </c>
       <c r="R38" t="n">
-        <v>7006716</v>
+        <v>7006694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -2280,10 +2280,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122361037</v>
+        <v>122355606</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2296,37 +2296,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494456</v>
+        <v>494524</v>
       </c>
       <c r="R14" t="n">
-        <v>7006360</v>
+        <v>7006571</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2358,6 +2368,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2384,12 +2399,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2407,10 +2422,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357658</v>
+        <v>122361037</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2423,47 +2438,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494515</v>
+        <v>494456</v>
       </c>
       <c r="R15" t="n">
-        <v>7006545</v>
+        <v>7006360</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2495,11 +2500,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2549,7 +2549,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122355606</v>
+        <v>122357658</v>
       </c>
       <c r="B16" t="n">
         <v>57399</v>
@@ -2595,14 +2595,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494524</v>
+        <v>494515</v>
       </c>
       <c r="R16" t="n">
-        <v>7006571</v>
+        <v>7006545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3368,10 +3368,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122364537</v>
+        <v>122360161</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3384,49 +3384,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494454</v>
+        <v>494380</v>
       </c>
       <c r="R22" t="n">
-        <v>7006579</v>
+        <v>7006419</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3460,7 +3448,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3477,29 +3465,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3517,10 +3500,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122360161</v>
+        <v>122364537</v>
       </c>
       <c r="B23" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3533,37 +3516,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494380</v>
+        <v>494454</v>
       </c>
       <c r="R23" t="n">
-        <v>7006419</v>
+        <v>7006579</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3597,7 +3592,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3614,24 +3609,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122355645</v>
+        <v>122359111</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,17 +721,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494521</v>
+        <v>494496</v>
       </c>
       <c r="R2" t="n">
-        <v>7006584</v>
+        <v>7006482</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,6 +763,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,6 +780,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122357683</v>
+        <v>122354497</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,42 +833,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494501</v>
+        <v>494602</v>
       </c>
       <c r="R3" t="n">
-        <v>7006553</v>
+        <v>7006702</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,6 +905,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -905,12 +936,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360218</v>
+        <v>122357863</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,34 +975,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494394</v>
+        <v>494497</v>
       </c>
       <c r="R4" t="n">
-        <v>7006412</v>
+        <v>7006523</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,26 +1063,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1055,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122361119</v>
+        <v>122357683</v>
       </c>
       <c r="B5" t="n">
-        <v>79737</v>
+        <v>90857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,27 +1096,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1100,13 +1125,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494460</v>
+        <v>494501</v>
       </c>
       <c r="R5" t="n">
-        <v>7006357</v>
+        <v>7006553</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,11 +1163,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1159,22 +1179,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1192,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122354497</v>
+        <v>122361005</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,47 +1228,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494602</v>
+        <v>494444</v>
       </c>
       <c r="R6" t="n">
-        <v>7006702</v>
+        <v>7006335</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1280,11 +1290,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1311,12 +1316,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,7 +1339,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359111</v>
+        <v>122357658</v>
       </c>
       <c r="B7" t="n">
         <v>57399</v>
@@ -1384,13 +1389,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494496</v>
+        <v>494515</v>
       </c>
       <c r="R7" t="n">
-        <v>7006482</v>
+        <v>7006545</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1429,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,12 +1448,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1458,7 +1463,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,10 +1481,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122359011</v>
+        <v>122364729</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,37 +1497,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494502</v>
+        <v>494499</v>
       </c>
       <c r="R8" t="n">
-        <v>7006489</v>
+        <v>7006492</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1554,6 +1571,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1568,6 +1590,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1580,12 +1607,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1603,10 +1630,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361274</v>
+        <v>122364318</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1619,37 +1646,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494472</v>
+        <v>494511</v>
       </c>
       <c r="R9" t="n">
-        <v>7006382</v>
+        <v>7006626</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1683,7 +1718,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,6 +1735,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1712,12 +1752,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1735,10 +1775,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122361005</v>
+        <v>122355822</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,34 +1791,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494444</v>
+        <v>494487</v>
       </c>
       <c r="R10" t="n">
-        <v>7006335</v>
+        <v>7006560</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1813,6 +1863,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1839,12 +1894,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1862,10 +1917,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122359691</v>
+        <v>122364537</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1878,37 +1933,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494410</v>
+        <v>494454</v>
       </c>
       <c r="R11" t="n">
-        <v>7006434</v>
+        <v>7006579</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1940,6 +2007,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1954,6 +2026,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1966,12 +2043,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1989,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122364212</v>
+        <v>122361119</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2005,49 +2082,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494582</v>
+        <v>494460</v>
       </c>
       <c r="R12" t="n">
-        <v>7006726</v>
+        <v>7006357</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2081,7 +2151,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2098,29 +2168,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2138,10 +2203,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122355822</v>
+        <v>122355540</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2154,47 +2219,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494487</v>
+        <v>494535</v>
       </c>
       <c r="R13" t="n">
-        <v>7006560</v>
+        <v>7006574</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2226,11 +2281,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2257,12 +2307,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2280,10 +2330,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122355606</v>
+        <v>122359011</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2296,44 +2346,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494524</v>
+        <v>494502</v>
       </c>
       <c r="R14" t="n">
-        <v>7006571</v>
+        <v>7006489</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2368,11 +2408,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2399,12 +2434,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2422,7 +2457,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122361037</v>
+        <v>122360218</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2462,13 +2497,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494456</v>
+        <v>494394</v>
       </c>
       <c r="R15" t="n">
-        <v>7006360</v>
+        <v>7006412</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2526,12 +2561,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2549,10 +2584,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357658</v>
+        <v>122364212</v>
       </c>
       <c r="B16" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2565,16 +2600,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2583,6 +2618,8 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2595,17 +2632,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494515</v>
+        <v>494582</v>
       </c>
       <c r="R16" t="n">
-        <v>7006545</v>
+        <v>7006726</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2639,7 +2676,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2656,6 +2693,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2668,12 +2710,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2691,10 +2733,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122364729</v>
+        <v>122355645</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2707,29 +2749,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2739,17 +2783,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494499</v>
+        <v>494521</v>
       </c>
       <c r="R17" t="n">
-        <v>7006492</v>
+        <v>7006584</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2781,11 +2825,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2798,31 +2837,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2840,10 +2854,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122360500</v>
+        <v>122360599</v>
       </c>
       <c r="B18" t="n">
-        <v>79773</v>
+        <v>79737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2852,43 +2866,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494402</v>
+        <v>494411</v>
       </c>
       <c r="R18" t="n">
-        <v>7006360</v>
+        <v>7006366</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2921,6 +2930,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2972,10 +2986,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122361219</v>
+        <v>122360500</v>
       </c>
       <c r="B19" t="n">
-        <v>79738</v>
+        <v>79773</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2984,31 +2998,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3017,13 +3031,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494464</v>
+        <v>494402</v>
       </c>
       <c r="R19" t="n">
-        <v>7006354</v>
+        <v>7006360</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3055,11 +3069,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3086,12 +3095,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3109,7 +3118,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122355540</v>
+        <v>122359691</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -3145,14 +3154,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494535</v>
+        <v>494410</v>
       </c>
       <c r="R20" t="n">
-        <v>7006574</v>
+        <v>7006434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3368,10 +3377,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122360161</v>
+        <v>122361037</v>
       </c>
       <c r="B22" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3384,21 +3393,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3408,13 +3417,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494380</v>
+        <v>494456</v>
       </c>
       <c r="R22" t="n">
-        <v>7006419</v>
+        <v>7006360</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3446,11 +3455,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3467,22 +3471,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3500,10 +3504,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122364537</v>
+        <v>122361274</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3516,49 +3520,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494454</v>
+        <v>494472</v>
       </c>
       <c r="R23" t="n">
-        <v>7006579</v>
+        <v>7006382</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3592,7 +3584,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3609,11 +3601,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3626,12 +3613,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3649,10 +3636,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122355933</v>
+        <v>122355606</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3665,37 +3652,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494462</v>
+        <v>494524</v>
       </c>
       <c r="R24" t="n">
-        <v>7006583</v>
+        <v>7006571</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3727,6 +3724,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3753,12 +3755,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3776,10 +3778,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122360599</v>
+        <v>122360113</v>
       </c>
       <c r="B25" t="n">
-        <v>79737</v>
+        <v>79766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3788,38 +3790,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494411</v>
+        <v>494392</v>
       </c>
       <c r="R25" t="n">
-        <v>7006366</v>
+        <v>7006448</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3852,11 +3859,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3908,10 +3910,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122360113</v>
+        <v>122355933</v>
       </c>
       <c r="B26" t="n">
-        <v>79766</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3920,46 +3922,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494392</v>
+        <v>494462</v>
       </c>
       <c r="R26" t="n">
-        <v>7006448</v>
+        <v>7006583</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4007,22 +4004,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4040,10 +4037,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122357863</v>
+        <v>122361219</v>
       </c>
       <c r="B27" t="n">
-        <v>57536</v>
+        <v>79738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4056,36 +4053,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4094,13 +4082,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494497</v>
+        <v>494464</v>
       </c>
       <c r="R27" t="n">
-        <v>7006523</v>
+        <v>7006354</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4132,6 +4120,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4144,6 +4137,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4161,10 +4174,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122364318</v>
+        <v>122360161</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4177,45 +4190,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494511</v>
+        <v>494380</v>
       </c>
       <c r="R28" t="n">
-        <v>7006626</v>
+        <v>7006419</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4249,7 +4254,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4266,29 +4271,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4448,10 +4448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122407975</v>
+        <v>122408149</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4464,34 +4464,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494572</v>
+        <v>494574</v>
       </c>
       <c r="R30" t="n">
-        <v>7006632</v>
+        <v>7006638</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4526,6 +4531,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4552,12 +4562,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4575,7 +4585,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406516</v>
+        <v>122406373</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -4615,10 +4625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494604</v>
+        <v>494674</v>
       </c>
       <c r="R31" t="n">
-        <v>7006665</v>
+        <v>7006716</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4679,12 +4689,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4702,10 +4712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122407671</v>
+        <v>122406983</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4718,44 +4728,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494534</v>
+        <v>494621</v>
       </c>
       <c r="R32" t="n">
-        <v>7006518</v>
+        <v>7006636</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4790,11 +4790,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4821,12 +4816,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4844,10 +4839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122407942</v>
+        <v>122406150</v>
       </c>
       <c r="B33" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4860,44 +4855,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494566</v>
+        <v>494722</v>
       </c>
       <c r="R33" t="n">
-        <v>7006630</v>
+        <v>7006694</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4932,11 +4917,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4953,22 +4933,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4986,7 +4966,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122406983</v>
+        <v>122405719</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -5026,10 +5006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494621</v>
+        <v>494740</v>
       </c>
       <c r="R34" t="n">
-        <v>7006636</v>
+        <v>7006719</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5113,10 +5093,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122408149</v>
+        <v>122407975</v>
       </c>
       <c r="B35" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5129,39 +5109,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494574</v>
+        <v>494572</v>
       </c>
       <c r="R35" t="n">
-        <v>7006638</v>
+        <v>7006632</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5196,11 +5171,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5227,12 +5197,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5250,7 +5220,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122406373</v>
+        <v>122406516</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -5290,10 +5260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494674</v>
+        <v>494604</v>
       </c>
       <c r="R36" t="n">
-        <v>7006716</v>
+        <v>7006665</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5354,12 +5324,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5377,10 +5347,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122405719</v>
+        <v>122407671</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5393,34 +5363,44 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494740</v>
+        <v>494534</v>
       </c>
       <c r="R37" t="n">
-        <v>7006719</v>
+        <v>7006518</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5455,6 +5435,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov granstam.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5481,12 +5466,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5504,10 +5489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122406150</v>
+        <v>122407942</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5520,34 +5505,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494722</v>
+        <v>494566</v>
       </c>
       <c r="R38" t="n">
-        <v>7006694</v>
+        <v>7006630</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5582,6 +5577,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5598,22 +5598,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122361005</v>
+        <v>122357658</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,37 +1228,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494444</v>
+        <v>494515</v>
       </c>
       <c r="R6" t="n">
-        <v>7006335</v>
+        <v>7006545</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1290,6 +1300,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1316,12 +1331,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1339,10 +1354,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357658</v>
+        <v>122361005</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1355,47 +1370,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494515</v>
+        <v>494444</v>
       </c>
       <c r="R7" t="n">
-        <v>7006545</v>
+        <v>7006335</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1427,11 +1432,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122361119</v>
+        <v>122355540</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2082,42 +2082,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494460</v>
+        <v>494535</v>
       </c>
       <c r="R12" t="n">
-        <v>7006357</v>
+        <v>7006574</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2149,11 +2144,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2170,22 +2160,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2203,7 +2193,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122355540</v>
+        <v>122359011</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -2239,14 +2229,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494535</v>
+        <v>494502</v>
       </c>
       <c r="R13" t="n">
-        <v>7006574</v>
+        <v>7006489</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2330,10 +2320,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122359011</v>
+        <v>122361119</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2346,37 +2336,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494502</v>
+        <v>494460</v>
       </c>
       <c r="R14" t="n">
-        <v>7006489</v>
+        <v>7006357</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2408,6 +2403,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2424,22 +2424,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359111</v>
+        <v>122361037</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494496</v>
+        <v>494456</v>
       </c>
       <c r="R2" t="n">
-        <v>7006482</v>
+        <v>7006360</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,11 +753,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,22 +769,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122354497</v>
+        <v>122355606</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -853,7 +838,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -867,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494602</v>
+        <v>494524</v>
       </c>
       <c r="R3" t="n">
-        <v>7006702</v>
+        <v>7006571</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Färska hackspår/födosökspår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122357863</v>
+        <v>122364212</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,31 +960,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1009,17 +992,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494497</v>
+        <v>494582</v>
       </c>
       <c r="R4" t="n">
-        <v>7006523</v>
+        <v>7006726</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1051,6 +1034,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1063,6 +1051,31 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,10 +1093,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122357683</v>
+        <v>122360500</v>
       </c>
       <c r="B5" t="n">
-        <v>90857</v>
+        <v>79773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,31 +1105,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1125,10 +1138,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494501</v>
+        <v>494402</v>
       </c>
       <c r="R5" t="n">
-        <v>7006553</v>
+        <v>7006360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1179,22 +1192,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1212,10 +1225,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122357658</v>
+        <v>122359011</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,44 +1241,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494515</v>
+        <v>494502</v>
       </c>
       <c r="R6" t="n">
-        <v>7006545</v>
+        <v>7006489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1300,11 +1303,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1331,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1354,7 +1352,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122361005</v>
+        <v>122361274</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1394,13 +1392,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494444</v>
+        <v>494472</v>
       </c>
       <c r="R7" t="n">
-        <v>7006335</v>
+        <v>7006382</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1430,6 +1428,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1481,10 +1484,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122364729</v>
+        <v>122360490</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>79766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1493,53 +1496,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494499</v>
+        <v>494402</v>
       </c>
       <c r="R8" t="n">
-        <v>7006492</v>
+        <v>7006360</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1571,11 +1567,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1590,29 +1581,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1630,10 +1616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122364318</v>
+        <v>122357658</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1646,16 +1632,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1664,27 +1650,29 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494511</v>
+        <v>494515</v>
       </c>
       <c r="R9" t="n">
-        <v>7006626</v>
+        <v>7006545</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1718,7 +1706,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1735,11 +1723,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1752,12 +1735,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1775,10 +1758,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122355822</v>
+        <v>122360161</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1791,44 +1774,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494487</v>
+        <v>494380</v>
       </c>
       <c r="R10" t="n">
-        <v>7006560</v>
+        <v>7006419</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1865,7 +1838,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1884,22 +1857,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1917,10 +1890,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122364537</v>
+        <v>122357863</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1933,29 +1906,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1965,17 +1940,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494454</v>
+        <v>494497</v>
       </c>
       <c r="R11" t="n">
-        <v>7006579</v>
+        <v>7006523</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2007,11 +1982,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2024,31 +1994,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2066,10 +2011,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122355540</v>
+        <v>122360599</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2082,34 +2027,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494535</v>
+        <v>494411</v>
       </c>
       <c r="R12" t="n">
-        <v>7006574</v>
+        <v>7006366</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2144,6 +2089,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2160,22 +2110,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2193,10 +2143,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122359011</v>
+        <v>122364537</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2209,37 +2159,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494502</v>
+        <v>494454</v>
       </c>
       <c r="R13" t="n">
-        <v>7006489</v>
+        <v>7006579</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2271,6 +2233,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2285,6 +2252,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2297,12 +2269,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2457,10 +2429,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122360218</v>
+        <v>122355645</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2473,34 +2445,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494394</v>
+        <v>494521</v>
       </c>
       <c r="R15" t="n">
-        <v>7006412</v>
+        <v>7006584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2547,26 +2533,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2584,10 +2550,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122364212</v>
+        <v>122355540</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2600,49 +2566,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494582</v>
+        <v>494535</v>
       </c>
       <c r="R16" t="n">
-        <v>7006726</v>
+        <v>7006574</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2674,11 +2628,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2693,11 +2642,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2710,12 +2654,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2733,10 +2677,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122355645</v>
+        <v>122364318</v>
       </c>
       <c r="B17" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2749,51 +2693,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494521</v>
+        <v>494511</v>
       </c>
       <c r="R17" t="n">
-        <v>7006584</v>
+        <v>7006626</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2825,6 +2763,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2837,6 +2780,31 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2854,10 +2822,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122360599</v>
+        <v>122361005</v>
       </c>
       <c r="B18" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2870,21 +2838,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2894,13 +2862,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494411</v>
+        <v>494444</v>
       </c>
       <c r="R18" t="n">
-        <v>7006366</v>
+        <v>7006335</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2932,11 +2900,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2953,22 +2916,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2986,10 +2949,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122360500</v>
+        <v>122360218</v>
       </c>
       <c r="B19" t="n">
-        <v>79773</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2998,43 +2961,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494402</v>
+        <v>494394</v>
       </c>
       <c r="R19" t="n">
-        <v>7006360</v>
+        <v>7006412</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3085,22 +3043,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3118,7 +3076,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122359691</v>
+        <v>122355933</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -3158,13 +3116,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494410</v>
+        <v>494462</v>
       </c>
       <c r="R20" t="n">
-        <v>7006434</v>
+        <v>7006583</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3245,10 +3203,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122360490</v>
+        <v>122355822</v>
       </c>
       <c r="B21" t="n">
-        <v>79766</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3257,31 +3215,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3290,10 +3253,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494402</v>
+        <v>494487</v>
       </c>
       <c r="R21" t="n">
-        <v>7006360</v>
+        <v>7006560</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3328,6 +3291,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3344,22 +3312,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3377,10 +3345,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122361037</v>
+        <v>122360113</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>79766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3389,41 +3357,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494456</v>
+        <v>494392</v>
       </c>
       <c r="R22" t="n">
-        <v>7006360</v>
+        <v>7006448</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3471,22 +3444,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3504,10 +3477,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122361274</v>
+        <v>122357683</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3520,34 +3493,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494472</v>
+        <v>494501</v>
       </c>
       <c r="R23" t="n">
-        <v>7006382</v>
+        <v>7006553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3582,11 +3560,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3613,12 +3586,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3636,7 +3609,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122355606</v>
+        <v>122354497</v>
       </c>
       <c r="B24" t="n">
         <v>57399</v>
@@ -3672,7 +3645,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3686,13 +3659,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494524</v>
+        <v>494602</v>
       </c>
       <c r="R24" t="n">
-        <v>7006571</v>
+        <v>7006702</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3726,7 +3699,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3755,12 +3728,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3778,10 +3751,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122360113</v>
+        <v>122361219</v>
       </c>
       <c r="B25" t="n">
-        <v>79766</v>
+        <v>79738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3790,31 +3763,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3823,13 +3796,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494392</v>
+        <v>494464</v>
       </c>
       <c r="R25" t="n">
-        <v>7006448</v>
+        <v>7006354</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3861,6 +3834,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3887,12 +3865,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3910,10 +3888,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122355933</v>
+        <v>122359111</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3926,37 +3904,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494462</v>
+        <v>494496</v>
       </c>
       <c r="R26" t="n">
-        <v>7006583</v>
+        <v>7006482</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3988,6 +3976,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4004,22 +3997,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4037,10 +4030,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122361219</v>
+        <v>122364729</v>
       </c>
       <c r="B27" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4053,42 +4046,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494464</v>
+        <v>494499</v>
       </c>
       <c r="R27" t="n">
-        <v>7006354</v>
+        <v>7006492</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4139,24 +4139,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4174,10 +4179,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122360161</v>
+        <v>122359691</v>
       </c>
       <c r="B28" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4190,21 +4195,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4214,13 +4219,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494380</v>
+        <v>494410</v>
       </c>
       <c r="R28" t="n">
-        <v>7006419</v>
+        <v>7006434</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4252,11 +4257,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4273,22 +4273,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122407432</v>
+        <v>122407975</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4322,44 +4322,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494548</v>
+        <v>494572</v>
       </c>
       <c r="R29" t="n">
-        <v>7006529</v>
+        <v>7006632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4394,11 +4384,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4425,12 +4410,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4448,10 +4433,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122408149</v>
+        <v>122407432</v>
       </c>
       <c r="B30" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4464,39 +4449,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494574</v>
+        <v>494548</v>
       </c>
       <c r="R30" t="n">
-        <v>7006638</v>
+        <v>7006529</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4533,7 +4523,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4562,12 +4552,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4585,10 +4575,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406373</v>
+        <v>122407671</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4601,34 +4591,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494674</v>
+        <v>494534</v>
       </c>
       <c r="R31" t="n">
-        <v>7006716</v>
+        <v>7006518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4663,6 +4663,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov granstam.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4689,12 +4694,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4712,10 +4717,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122406983</v>
+        <v>122408149</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4728,34 +4733,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494621</v>
+        <v>494574</v>
       </c>
       <c r="R32" t="n">
-        <v>7006636</v>
+        <v>7006638</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4790,6 +4800,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4816,12 +4831,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4839,7 +4854,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122406150</v>
+        <v>122406373</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -4879,10 +4894,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494722</v>
+        <v>494674</v>
       </c>
       <c r="R33" t="n">
-        <v>7006694</v>
+        <v>7006716</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4943,12 +4958,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4966,7 +4981,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122405719</v>
+        <v>122406150</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -5006,10 +5021,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494740</v>
+        <v>494722</v>
       </c>
       <c r="R34" t="n">
-        <v>7006719</v>
+        <v>7006694</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5093,10 +5108,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407975</v>
+        <v>122407942</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5109,34 +5124,44 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494572</v>
+        <v>494566</v>
       </c>
       <c r="R35" t="n">
-        <v>7006632</v>
+        <v>7006630</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5171,6 +5196,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5187,22 +5217,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5220,7 +5250,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122406516</v>
+        <v>122406983</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -5260,10 +5290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494604</v>
+        <v>494621</v>
       </c>
       <c r="R36" t="n">
-        <v>7006665</v>
+        <v>7006636</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5347,10 +5377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122407671</v>
+        <v>122405719</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5363,44 +5393,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494534</v>
+        <v>494740</v>
       </c>
       <c r="R37" t="n">
-        <v>7006518</v>
+        <v>7006719</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5435,11 +5455,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5466,12 +5481,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5489,10 +5504,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122407942</v>
+        <v>122406516</v>
       </c>
       <c r="B38" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5505,44 +5520,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494566</v>
+        <v>494604</v>
       </c>
       <c r="R38" t="n">
-        <v>7006630</v>
+        <v>7006665</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5577,11 +5582,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5598,22 +5598,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361037</v>
+        <v>122359011</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494456</v>
+        <v>494502</v>
       </c>
       <c r="R2" t="n">
-        <v>7006360</v>
+        <v>7006489</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122355606</v>
+        <v>122355822</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494524</v>
+        <v>494487</v>
       </c>
       <c r="R3" t="n">
-        <v>7006571</v>
+        <v>7006560</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122364212</v>
+        <v>122357658</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -978,8 +978,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -992,17 +990,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494582</v>
+        <v>494515</v>
       </c>
       <c r="R4" t="n">
-        <v>7006726</v>
+        <v>7006545</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1036,7 +1034,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,11 +1051,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1070,12 +1063,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1093,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360500</v>
+        <v>122355606</v>
       </c>
       <c r="B5" t="n">
-        <v>79773</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1105,43 +1098,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494402</v>
+        <v>494524</v>
       </c>
       <c r="R5" t="n">
-        <v>7006360</v>
+        <v>7006571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,6 +1174,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1192,22 +1195,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1225,7 +1228,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359011</v>
+        <v>122355933</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1265,13 +1268,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494502</v>
+        <v>494462</v>
       </c>
       <c r="R6" t="n">
-        <v>7006489</v>
+        <v>7006583</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1352,10 +1355,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122361274</v>
+        <v>122364537</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,37 +1371,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494472</v>
+        <v>494454</v>
       </c>
       <c r="R7" t="n">
-        <v>7006382</v>
+        <v>7006579</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1432,7 +1447,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,6 +1464,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1461,12 +1481,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1484,10 +1504,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122360490</v>
+        <v>122364318</v>
       </c>
       <c r="B8" t="n">
-        <v>79766</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1496,46 +1516,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494402</v>
+        <v>494511</v>
       </c>
       <c r="R8" t="n">
-        <v>7006360</v>
+        <v>7006626</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1567,6 +1590,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1581,24 +1609,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1616,10 +1649,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122357658</v>
+        <v>122360113</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>79766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1628,36 +1661,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1666,10 +1694,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494515</v>
+        <v>494392</v>
       </c>
       <c r="R9" t="n">
-        <v>7006545</v>
+        <v>7006448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1704,11 +1732,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1725,22 +1748,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1758,7 +1781,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122360161</v>
+        <v>122361119</v>
       </c>
       <c r="B10" t="n">
         <v>79737</v>
@@ -1792,19 +1815,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494380</v>
+        <v>494460</v>
       </c>
       <c r="R10" t="n">
-        <v>7006419</v>
+        <v>7006357</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1838,7 +1866,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1890,10 +1918,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357863</v>
+        <v>122361005</v>
       </c>
       <c r="B11" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1906,51 +1934,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494497</v>
+        <v>494444</v>
       </c>
       <c r="R11" t="n">
-        <v>7006523</v>
+        <v>7006335</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1994,6 +2008,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2011,10 +2045,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122360599</v>
+        <v>122354497</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2027,37 +2061,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494411</v>
+        <v>494602</v>
       </c>
       <c r="R12" t="n">
-        <v>7006366</v>
+        <v>7006702</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2091,7 +2135,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2110,22 +2154,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2143,10 +2187,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122364537</v>
+        <v>122360218</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2159,49 +2203,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494454</v>
+        <v>494394</v>
       </c>
       <c r="R13" t="n">
-        <v>7006579</v>
+        <v>7006412</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2233,11 +2265,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2252,11 +2279,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2269,12 +2291,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2292,10 +2314,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122361119</v>
+        <v>122360490</v>
       </c>
       <c r="B14" t="n">
-        <v>79737</v>
+        <v>79766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2304,31 +2326,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2337,13 +2359,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494460</v>
+        <v>494402</v>
       </c>
       <c r="R14" t="n">
-        <v>7006357</v>
+        <v>7006360</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2373,11 +2395,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2429,10 +2446,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122355645</v>
+        <v>122359691</v>
       </c>
       <c r="B15" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2445,48 +2462,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494521</v>
+        <v>494410</v>
       </c>
       <c r="R15" t="n">
-        <v>7006584</v>
+        <v>7006434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2533,6 +2536,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2550,10 +2573,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122355540</v>
+        <v>122360500</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>79773</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2562,38 +2585,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494535</v>
+        <v>494402</v>
       </c>
       <c r="R16" t="n">
-        <v>7006574</v>
+        <v>7006360</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2644,22 +2672,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2677,10 +2705,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122364318</v>
+        <v>122355645</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2693,45 +2721,51 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494511</v>
+        <v>494521</v>
       </c>
       <c r="R17" t="n">
-        <v>7006626</v>
+        <v>7006584</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2763,11 +2797,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2780,31 +2809,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2822,10 +2826,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122361005</v>
+        <v>122360161</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2838,21 +2842,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2862,10 +2866,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494444</v>
+        <v>494380</v>
       </c>
       <c r="R18" t="n">
-        <v>7006335</v>
+        <v>7006419</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2900,6 +2904,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2916,22 +2925,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2949,10 +2958,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122360218</v>
+        <v>122360599</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2965,21 +2974,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2989,10 +2998,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494394</v>
+        <v>494411</v>
       </c>
       <c r="R19" t="n">
-        <v>7006412</v>
+        <v>7006366</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3027,6 +3036,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3043,22 +3057,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3076,10 +3090,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122355933</v>
+        <v>122357863</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3092,37 +3106,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494462</v>
+        <v>494497</v>
       </c>
       <c r="R20" t="n">
-        <v>7006583</v>
+        <v>7006523</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3166,26 +3194,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3203,10 +3211,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122355822</v>
+        <v>122361037</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3219,47 +3227,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494487</v>
+        <v>494456</v>
       </c>
       <c r="R21" t="n">
-        <v>7006560</v>
+        <v>7006360</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3291,11 +3289,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3322,12 +3315,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3345,10 +3338,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122360113</v>
+        <v>122361219</v>
       </c>
       <c r="B22" t="n">
-        <v>79766</v>
+        <v>79738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3357,31 +3350,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3390,13 +3383,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494392</v>
+        <v>494464</v>
       </c>
       <c r="R22" t="n">
-        <v>7006448</v>
+        <v>7006354</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3428,6 +3421,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3454,12 +3452,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3477,10 +3475,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122357683</v>
+        <v>122364729</v>
       </c>
       <c r="B23" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3493,42 +3491,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494501</v>
+        <v>494499</v>
       </c>
       <c r="R23" t="n">
-        <v>7006553</v>
+        <v>7006492</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3560,6 +3565,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3574,6 +3584,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3586,12 +3601,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3609,10 +3624,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122354497</v>
+        <v>122357683</v>
       </c>
       <c r="B24" t="n">
-        <v>57399</v>
+        <v>90851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3625,47 +3640,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494602</v>
+        <v>494501</v>
       </c>
       <c r="R24" t="n">
-        <v>7006702</v>
+        <v>7006553</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3697,11 +3707,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3728,12 +3733,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3751,10 +3756,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122361219</v>
+        <v>122364212</v>
       </c>
       <c r="B25" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3767,42 +3772,49 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494464</v>
+        <v>494582</v>
       </c>
       <c r="R25" t="n">
-        <v>7006354</v>
+        <v>7006726</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3836,7 +3848,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3853,24 +3865,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3888,10 +3905,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122359111</v>
+        <v>122355540</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3904,47 +3921,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494496</v>
+        <v>494535</v>
       </c>
       <c r="R26" t="n">
-        <v>7006482</v>
+        <v>7006574</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3976,11 +3983,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3997,22 +3999,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4030,10 +4032,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122364729</v>
+        <v>122359111</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4046,16 +4048,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4064,8 +4066,6 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4078,17 +4078,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494499</v>
+        <v>494496</v>
       </c>
       <c r="R27" t="n">
-        <v>7006492</v>
+        <v>7006482</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4139,29 +4139,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4179,7 +4174,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122359691</v>
+        <v>122361274</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -4219,10 +4214,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494410</v>
+        <v>494472</v>
       </c>
       <c r="R28" t="n">
-        <v>7006434</v>
+        <v>7006382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4255,6 +4250,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4306,7 +4306,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122407975</v>
+        <v>122406373</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494572</v>
+        <v>494674</v>
       </c>
       <c r="R29" t="n">
-        <v>7006632</v>
+        <v>7006716</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122407432</v>
+        <v>122407671</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -4469,7 +4469,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494548</v>
+        <v>494534</v>
       </c>
       <c r="R30" t="n">
-        <v>7006529</v>
+        <v>7006518</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska ringhack på en relativt grov granstam.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4575,10 +4575,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122407671</v>
+        <v>122406983</v>
       </c>
       <c r="B31" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4591,44 +4591,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494534</v>
+        <v>494621</v>
       </c>
       <c r="R31" t="n">
-        <v>7006518</v>
+        <v>7006636</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4663,11 +4653,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4694,12 +4679,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4717,10 +4702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122408149</v>
+        <v>122406150</v>
       </c>
       <c r="B32" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4733,39 +4718,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494574</v>
+        <v>494722</v>
       </c>
       <c r="R32" t="n">
-        <v>7006638</v>
+        <v>7006694</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4800,11 +4780,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4831,12 +4806,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4854,10 +4829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122406373</v>
+        <v>122408149</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4870,34 +4845,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494674</v>
+        <v>494574</v>
       </c>
       <c r="R33" t="n">
-        <v>7006716</v>
+        <v>7006638</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4932,6 +4912,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4958,12 +4943,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4981,7 +4966,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122406150</v>
+        <v>122405719</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -5021,10 +5006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494722</v>
+        <v>494740</v>
       </c>
       <c r="R34" t="n">
-        <v>7006694</v>
+        <v>7006719</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5108,10 +5093,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407942</v>
+        <v>122407975</v>
       </c>
       <c r="B35" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5124,44 +5109,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494566</v>
+        <v>494572</v>
       </c>
       <c r="R35" t="n">
-        <v>7006630</v>
+        <v>7006632</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5196,11 +5171,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5217,22 +5187,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5250,10 +5220,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122406983</v>
+        <v>122407942</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5266,34 +5236,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494621</v>
+        <v>494566</v>
       </c>
       <c r="R36" t="n">
-        <v>7006636</v>
+        <v>7006630</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5328,6 +5308,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5344,22 +5329,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5377,10 +5362,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122405719</v>
+        <v>122407432</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5393,34 +5378,44 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494740</v>
+        <v>494548</v>
       </c>
       <c r="R37" t="n">
-        <v>7006719</v>
+        <v>7006529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5455,6 +5450,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5481,12 +5481,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359011</v>
+        <v>122360500</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>79774</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494502</v>
+        <v>494402</v>
       </c>
       <c r="R2" t="n">
-        <v>7006489</v>
+        <v>7006360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,22 +774,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122355822</v>
+        <v>122355606</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +823,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,7 +843,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -848,17 +853,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494487</v>
+        <v>494524</v>
       </c>
       <c r="R3" t="n">
-        <v>7006560</v>
+        <v>7006571</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska hackspår/födosökspår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +926,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122357658</v>
+        <v>122360218</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,44 +965,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494515</v>
+        <v>494394</v>
       </c>
       <c r="R4" t="n">
-        <v>7006545</v>
+        <v>7006412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1032,11 +1027,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1063,12 +1053,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1086,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122355606</v>
+        <v>122359011</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,44 +1092,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494524</v>
+        <v>494502</v>
       </c>
       <c r="R5" t="n">
-        <v>7006571</v>
+        <v>7006489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1174,11 +1154,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1205,12 +1180,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1228,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122355933</v>
+        <v>122357683</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1244,37 +1219,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494462</v>
+        <v>494501</v>
       </c>
       <c r="R6" t="n">
-        <v>7006583</v>
+        <v>7006553</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1332,12 +1312,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1355,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122364537</v>
+        <v>122357863</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1371,29 +1351,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1403,17 +1385,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494454</v>
+        <v>494497</v>
       </c>
       <c r="R7" t="n">
-        <v>7006579</v>
+        <v>7006523</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1445,11 +1427,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1462,31 +1439,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1504,10 +1456,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122364318</v>
+        <v>122360161</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1520,45 +1472,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494511</v>
+        <v>494380</v>
       </c>
       <c r="R8" t="n">
-        <v>7006626</v>
+        <v>7006419</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1592,7 +1536,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1609,29 +1553,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1649,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122360113</v>
+        <v>122360490</v>
       </c>
       <c r="B9" t="n">
-        <v>79766</v>
+        <v>79767</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1694,13 +1633,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494392</v>
+        <v>494402</v>
       </c>
       <c r="R9" t="n">
-        <v>7006448</v>
+        <v>7006360</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1781,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122361119</v>
+        <v>122361005</v>
       </c>
       <c r="B10" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1797,42 +1736,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494460</v>
+        <v>494444</v>
       </c>
       <c r="R10" t="n">
-        <v>7006357</v>
+        <v>7006335</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1864,11 +1798,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1885,22 +1814,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1918,10 +1847,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122361005</v>
+        <v>122361219</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>79739</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1934,37 +1863,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494444</v>
+        <v>494464</v>
       </c>
       <c r="R11" t="n">
-        <v>7006335</v>
+        <v>7006354</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,6 +1930,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2012,22 +1951,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2045,10 +1984,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122354497</v>
+        <v>122357658</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2081,7 +2020,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2091,17 +2030,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494602</v>
+        <v>494515</v>
       </c>
       <c r="R12" t="n">
-        <v>7006702</v>
+        <v>7006545</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2135,7 +2074,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2164,12 +2103,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2187,10 +2126,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122360218</v>
+        <v>122355645</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57537</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2203,34 +2142,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494394</v>
+        <v>494521</v>
       </c>
       <c r="R13" t="n">
-        <v>7006412</v>
+        <v>7006584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2277,26 +2230,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2314,10 +2247,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122360490</v>
+        <v>122360113</v>
       </c>
       <c r="B14" t="n">
-        <v>79766</v>
+        <v>79767</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2359,13 +2292,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494402</v>
+        <v>494392</v>
       </c>
       <c r="R14" t="n">
-        <v>7006360</v>
+        <v>7006448</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2446,10 +2379,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122359691</v>
+        <v>122359111</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2462,37 +2395,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494410</v>
+        <v>494496</v>
       </c>
       <c r="R15" t="n">
-        <v>7006434</v>
+        <v>7006482</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2524,6 +2467,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2540,22 +2488,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2573,10 +2521,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122360500</v>
+        <v>122361037</v>
       </c>
       <c r="B16" t="n">
-        <v>79773</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2585,46 +2533,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494402</v>
+        <v>494456</v>
       </c>
       <c r="R16" t="n">
         <v>7006360</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2672,22 +2615,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2705,10 +2648,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122355645</v>
+        <v>122364212</v>
       </c>
       <c r="B17" t="n">
-        <v>57536</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2721,31 +2664,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2755,17 +2696,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494521</v>
+        <v>494582</v>
       </c>
       <c r="R17" t="n">
-        <v>7006584</v>
+        <v>7006726</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2797,6 +2738,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2809,6 +2755,31 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2826,10 +2797,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122360161</v>
+        <v>122364537</v>
       </c>
       <c r="B18" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2842,37 +2813,49 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494380</v>
+        <v>494454</v>
       </c>
       <c r="R18" t="n">
-        <v>7006419</v>
+        <v>7006579</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2906,7 +2889,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2923,24 +2906,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2958,10 +2946,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122360599</v>
+        <v>122355933</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2974,21 +2962,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2998,13 +2986,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494411</v>
+        <v>494462</v>
       </c>
       <c r="R19" t="n">
-        <v>7006366</v>
+        <v>7006583</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3036,11 +3024,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3057,22 +3040,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3090,10 +3073,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122357863</v>
+        <v>122361274</v>
       </c>
       <c r="B20" t="n">
-        <v>57536</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3106,48 +3089,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494497</v>
+        <v>494472</v>
       </c>
       <c r="R20" t="n">
-        <v>7006523</v>
+        <v>7006382</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3182,6 +3151,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3194,6 +3168,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3211,10 +3205,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122361037</v>
+        <v>122360599</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3227,21 +3221,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3251,13 +3245,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494456</v>
+        <v>494411</v>
       </c>
       <c r="R21" t="n">
-        <v>7006360</v>
+        <v>7006366</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3289,6 +3283,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3305,22 +3304,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3338,10 +3337,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122361219</v>
+        <v>122354497</v>
       </c>
       <c r="B22" t="n">
-        <v>79738</v>
+        <v>57400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3354,39 +3353,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494464</v>
+        <v>494602</v>
       </c>
       <c r="R22" t="n">
-        <v>7006354</v>
+        <v>7006702</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
@@ -3423,7 +3427,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3442,22 +3446,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3475,10 +3479,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122364729</v>
+        <v>122359691</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3491,49 +3495,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494499</v>
+        <v>494410</v>
       </c>
       <c r="R23" t="n">
-        <v>7006492</v>
+        <v>7006434</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3565,11 +3557,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3584,11 +3571,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3601,12 +3583,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3624,10 +3606,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122357683</v>
+        <v>122361119</v>
       </c>
       <c r="B24" t="n">
-        <v>90851</v>
+        <v>79738</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3640,27 +3622,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3669,13 +3651,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494501</v>
+        <v>494460</v>
       </c>
       <c r="R24" t="n">
-        <v>7006553</v>
+        <v>7006357</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3707,6 +3689,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3723,22 +3710,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3756,10 +3743,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122364212</v>
+        <v>122355540</v>
       </c>
       <c r="B25" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3772,49 +3759,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494582</v>
+        <v>494535</v>
       </c>
       <c r="R25" t="n">
-        <v>7006726</v>
+        <v>7006574</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3846,11 +3821,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3865,11 +3835,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3882,12 +3847,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3905,10 +3870,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122355540</v>
+        <v>122364318</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3921,37 +3886,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494535</v>
+        <v>494511</v>
       </c>
       <c r="R26" t="n">
-        <v>7006574</v>
+        <v>7006626</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3983,6 +3956,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3997,6 +3975,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ26" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4009,12 +3992,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4032,10 +4015,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122359111</v>
+        <v>122364729</v>
       </c>
       <c r="B27" t="n">
-        <v>57399</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4048,16 +4031,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4066,6 +4049,8 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4078,17 +4063,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494496</v>
+        <v>494499</v>
       </c>
       <c r="R27" t="n">
-        <v>7006482</v>
+        <v>7006492</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4122,7 +4107,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4139,24 +4124,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4174,10 +4164,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122361274</v>
+        <v>122355822</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4190,37 +4180,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494472</v>
+        <v>494487</v>
       </c>
       <c r="R28" t="n">
-        <v>7006382</v>
+        <v>7006560</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122406373</v>
+        <v>122406983</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494674</v>
+        <v>494621</v>
       </c>
       <c r="R29" t="n">
-        <v>7006716</v>
+        <v>7006636</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4436,7 +4436,7 @@
         <v>122407671</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406983</v>
+        <v>122407975</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494621</v>
+        <v>494572</v>
       </c>
       <c r="R31" t="n">
-        <v>7006636</v>
+        <v>7006632</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4702,10 +4702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122406150</v>
+        <v>122408149</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4718,34 +4718,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494722</v>
+        <v>494574</v>
       </c>
       <c r="R32" t="n">
-        <v>7006694</v>
+        <v>7006638</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4780,6 +4785,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4806,12 +4816,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4829,10 +4839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122408149</v>
+        <v>122407942</v>
       </c>
       <c r="B33" t="n">
-        <v>90851</v>
+        <v>57400</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4845,39 +4855,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494574</v>
+        <v>494566</v>
       </c>
       <c r="R33" t="n">
-        <v>7006638</v>
+        <v>7006630</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4914,7 +4929,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4933,12 +4948,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -4948,7 +4963,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4969,7 +4984,7 @@
         <v>122405719</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5093,10 +5108,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407975</v>
+        <v>122407432</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5109,34 +5124,44 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494572</v>
+        <v>494548</v>
       </c>
       <c r="R35" t="n">
-        <v>7006632</v>
+        <v>7006529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5171,6 +5196,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5197,12 +5227,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5220,10 +5250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122407942</v>
+        <v>122406150</v>
       </c>
       <c r="B36" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5236,44 +5266,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494566</v>
+        <v>494722</v>
       </c>
       <c r="R36" t="n">
-        <v>7006630</v>
+        <v>7006694</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5308,11 +5328,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5329,22 +5344,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5362,10 +5377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122407432</v>
+        <v>122406516</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5378,44 +5393,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494548</v>
+        <v>494604</v>
       </c>
       <c r="R37" t="n">
-        <v>7006529</v>
+        <v>7006665</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5450,11 +5455,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5481,12 +5481,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5504,10 +5504,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122406516</v>
+        <v>122406373</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494604</v>
+        <v>494674</v>
       </c>
       <c r="R38" t="n">
-        <v>7006665</v>
+        <v>7006716</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122357683</v>
+        <v>122357863</v>
       </c>
       <c r="B6" t="n">
-        <v>90852</v>
+        <v>57537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,27 +1219,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,10 +1257,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494501</v>
+        <v>494497</v>
       </c>
       <c r="R6" t="n">
-        <v>7006553</v>
+        <v>7006523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1298,26 +1307,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1324,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357863</v>
+        <v>122357683</v>
       </c>
       <c r="B7" t="n">
-        <v>57537</v>
+        <v>90852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,36 +1340,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1389,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494497</v>
+        <v>494501</v>
       </c>
       <c r="R7" t="n">
-        <v>7006523</v>
+        <v>7006553</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1439,6 +1419,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122407671</v>
+        <v>122407975</v>
       </c>
       <c r="B30" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4449,44 +4449,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494534</v>
+        <v>494572</v>
       </c>
       <c r="R30" t="n">
-        <v>7006518</v>
+        <v>7006632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4521,11 +4511,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4552,12 +4537,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4575,10 +4560,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122407975</v>
+        <v>122407671</v>
       </c>
       <c r="B31" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4591,34 +4576,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494572</v>
+        <v>494534</v>
       </c>
       <c r="R31" t="n">
-        <v>7006632</v>
+        <v>7006518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4653,6 +4648,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov granstam.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360500</v>
+        <v>122361119</v>
       </c>
       <c r="B2" t="n">
-        <v>79774</v>
+        <v>79741</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494402</v>
+        <v>494460</v>
       </c>
       <c r="R2" t="n">
-        <v>7006360</v>
+        <v>7006357</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122355606</v>
+        <v>122360490</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>79770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,51 +824,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494524</v>
+        <v>494402</v>
       </c>
       <c r="R3" t="n">
-        <v>7006571</v>
+        <v>7006360</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,11 +895,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -916,22 +911,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360218</v>
+        <v>122364212</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,37 +960,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494394</v>
+        <v>494582</v>
       </c>
       <c r="R4" t="n">
-        <v>7006412</v>
+        <v>7006726</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,6 +1034,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1041,6 +1053,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1053,12 +1070,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,10 +1093,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359011</v>
+        <v>122357863</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,34 +1109,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494502</v>
+        <v>494497</v>
       </c>
       <c r="R5" t="n">
-        <v>7006489</v>
+        <v>7006523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1166,26 +1197,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1214,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122357863</v>
+        <v>122355540</v>
       </c>
       <c r="B6" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,48 +1230,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494497</v>
+        <v>494535</v>
       </c>
       <c r="R6" t="n">
-        <v>7006523</v>
+        <v>7006574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1307,6 +1304,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1324,10 +1341,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357683</v>
+        <v>122360500</v>
       </c>
       <c r="B7" t="n">
-        <v>90852</v>
+        <v>79777</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,31 +1353,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1369,10 +1386,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494501</v>
+        <v>494402</v>
       </c>
       <c r="R7" t="n">
-        <v>7006553</v>
+        <v>7006360</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,22 +1440,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1459,7 +1476,7 @@
         <v>122360161</v>
       </c>
       <c r="B8" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1588,10 +1605,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122360490</v>
+        <v>122354497</v>
       </c>
       <c r="B9" t="n">
-        <v>79767</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1600,46 +1617,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494402</v>
+        <v>494602</v>
       </c>
       <c r="R9" t="n">
-        <v>7006360</v>
+        <v>7006702</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1671,6 +1693,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1687,22 +1714,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1720,10 +1747,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122361005</v>
+        <v>122357683</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,37 +1763,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494444</v>
+        <v>494501</v>
       </c>
       <c r="R10" t="n">
-        <v>7006335</v>
+        <v>7006553</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1824,12 +1856,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1847,10 +1879,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122361219</v>
+        <v>122359691</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1863,42 +1895,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494464</v>
+        <v>494410</v>
       </c>
       <c r="R11" t="n">
-        <v>7006354</v>
+        <v>7006434</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1930,11 +1957,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1951,22 +1973,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1984,10 +2006,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357658</v>
+        <v>122361005</v>
       </c>
       <c r="B12" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2000,47 +2022,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494515</v>
+        <v>494444</v>
       </c>
       <c r="R12" t="n">
-        <v>7006545</v>
+        <v>7006335</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2072,11 +2084,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2103,12 +2110,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2126,10 +2133,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122355645</v>
+        <v>122359011</v>
       </c>
       <c r="B13" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2142,48 +2149,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494521</v>
+        <v>494502</v>
       </c>
       <c r="R13" t="n">
-        <v>7006584</v>
+        <v>7006489</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2230,6 +2223,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2247,10 +2260,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122360113</v>
+        <v>122361219</v>
       </c>
       <c r="B14" t="n">
-        <v>79767</v>
+        <v>79742</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2259,31 +2272,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2292,13 +2305,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494392</v>
+        <v>494464</v>
       </c>
       <c r="R14" t="n">
-        <v>7006448</v>
+        <v>7006354</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2330,6 +2343,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2356,12 +2374,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2379,10 +2397,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122359111</v>
+        <v>122364537</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2395,16 +2413,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2413,9 +2431,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2425,17 +2445,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494496</v>
+        <v>494454</v>
       </c>
       <c r="R15" t="n">
-        <v>7006482</v>
+        <v>7006579</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2469,7 +2489,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2486,24 +2506,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2521,10 +2546,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122361037</v>
+        <v>122359111</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2537,37 +2562,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494456</v>
+        <v>494496</v>
       </c>
       <c r="R16" t="n">
-        <v>7006360</v>
+        <v>7006482</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2599,6 +2634,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2615,22 +2655,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2648,10 +2688,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122364212</v>
+        <v>122360599</v>
       </c>
       <c r="B17" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2664,49 +2704,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494582</v>
+        <v>494411</v>
       </c>
       <c r="R17" t="n">
-        <v>7006726</v>
+        <v>7006366</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2740,7 +2768,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2757,29 +2785,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2797,10 +2820,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122364537</v>
+        <v>122360113</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
+        <v>79770</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2809,53 +2832,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494454</v>
+        <v>494392</v>
       </c>
       <c r="R18" t="n">
-        <v>7006579</v>
+        <v>7006448</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2887,11 +2903,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2906,29 +2917,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2946,10 +2952,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122355933</v>
+        <v>122357658</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2962,37 +2968,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494462</v>
+        <v>494515</v>
       </c>
       <c r="R19" t="n">
-        <v>7006583</v>
+        <v>7006545</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3024,6 +3040,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3050,12 +3071,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3073,10 +3094,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122361274</v>
+        <v>122355822</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3089,37 +3110,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494472</v>
+        <v>494487</v>
       </c>
       <c r="R20" t="n">
-        <v>7006382</v>
+        <v>7006560</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3153,7 +3184,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3182,12 +3213,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3205,10 +3236,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122360599</v>
+        <v>122361037</v>
       </c>
       <c r="B21" t="n">
-        <v>79738</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3221,21 +3252,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3245,13 +3276,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494411</v>
+        <v>494456</v>
       </c>
       <c r="R21" t="n">
-        <v>7006366</v>
+        <v>7006360</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3283,11 +3314,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3304,22 +3330,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3337,10 +3363,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122354497</v>
+        <v>122355933</v>
       </c>
       <c r="B22" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3353,44 +3379,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494602</v>
+        <v>494462</v>
       </c>
       <c r="R22" t="n">
-        <v>7006702</v>
+        <v>7006583</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
@@ -3425,11 +3441,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3456,12 +3467,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3479,10 +3490,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122359691</v>
+        <v>122355606</v>
       </c>
       <c r="B23" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3495,34 +3506,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494410</v>
+        <v>494524</v>
       </c>
       <c r="R23" t="n">
-        <v>7006434</v>
+        <v>7006571</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3557,6 +3578,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3583,12 +3609,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3606,10 +3632,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122361119</v>
+        <v>122355645</v>
       </c>
       <c r="B24" t="n">
-        <v>79738</v>
+        <v>57537</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3622,42 +3648,51 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494460</v>
+        <v>494521</v>
       </c>
       <c r="R24" t="n">
-        <v>7006357</v>
+        <v>7006584</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3689,11 +3724,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3706,26 +3736,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3743,10 +3753,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122355540</v>
+        <v>122360218</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3779,14 +3789,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494535</v>
+        <v>494394</v>
       </c>
       <c r="R25" t="n">
-        <v>7006574</v>
+        <v>7006412</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3870,10 +3880,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122364318</v>
+        <v>122361274</v>
       </c>
       <c r="B26" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3886,45 +3896,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494511</v>
+        <v>494472</v>
       </c>
       <c r="R26" t="n">
-        <v>7006626</v>
+        <v>7006382</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3958,7 +3960,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3975,11 +3977,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3992,12 +3989,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4164,7 +4161,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122355822</v>
+        <v>122364318</v>
       </c>
       <c r="B28" t="n">
         <v>57384</v>
@@ -4198,29 +4195,27 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494487</v>
+        <v>494511</v>
       </c>
       <c r="R28" t="n">
-        <v>7006560</v>
+        <v>7006626</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4254,7 +4249,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4269,6 +4264,11 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4306,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122406983</v>
+        <v>122405719</v>
       </c>
       <c r="B29" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494621</v>
+        <v>494740</v>
       </c>
       <c r="R29" t="n">
-        <v>7006636</v>
+        <v>7006719</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4433,10 +4433,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122407975</v>
+        <v>122406373</v>
       </c>
       <c r="B30" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494572</v>
+        <v>494674</v>
       </c>
       <c r="R30" t="n">
-        <v>7006632</v>
+        <v>7006716</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122407671</v>
+        <v>122406150</v>
       </c>
       <c r="B31" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4576,44 +4576,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494534</v>
+        <v>494722</v>
       </c>
       <c r="R31" t="n">
-        <v>7006518</v>
+        <v>7006694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4648,11 +4638,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov granstam.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4679,12 +4664,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4702,10 +4687,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122408149</v>
+        <v>122407671</v>
       </c>
       <c r="B32" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4718,39 +4703,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494574</v>
+        <v>494534</v>
       </c>
       <c r="R32" t="n">
-        <v>7006638</v>
+        <v>7006518</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4787,7 +4777,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar.</t>
+          <t>Färska ringhack på en relativt grov granstam.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4816,12 +4806,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4839,10 +4829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122407942</v>
+        <v>122407432</v>
       </c>
       <c r="B33" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4855,16 +4845,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4875,7 +4865,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4885,14 +4875,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494566</v>
+        <v>494548</v>
       </c>
       <c r="R33" t="n">
-        <v>7006630</v>
+        <v>7006529</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4929,7 +4919,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4948,22 +4938,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4981,10 +4971,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122405719</v>
+        <v>122406983</v>
       </c>
       <c r="B34" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5021,10 +5011,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494740</v>
+        <v>494621</v>
       </c>
       <c r="R34" t="n">
-        <v>7006719</v>
+        <v>7006636</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5108,10 +5098,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407432</v>
+        <v>122407975</v>
       </c>
       <c r="B35" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5124,44 +5114,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494548</v>
+        <v>494572</v>
       </c>
       <c r="R35" t="n">
-        <v>7006529</v>
+        <v>7006632</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5196,11 +5176,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5227,12 +5202,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5250,10 +5225,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122406150</v>
+        <v>122406516</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5290,10 +5265,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494722</v>
+        <v>494604</v>
       </c>
       <c r="R36" t="n">
-        <v>7006694</v>
+        <v>7006665</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5377,10 +5352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122406516</v>
+        <v>122408149</v>
       </c>
       <c r="B37" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5393,34 +5368,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494604</v>
+        <v>494574</v>
       </c>
       <c r="R37" t="n">
-        <v>7006665</v>
+        <v>7006638</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5455,6 +5435,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5481,12 +5466,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5504,10 +5489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122406373</v>
+        <v>122407942</v>
       </c>
       <c r="B38" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5520,34 +5505,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494674</v>
+        <v>494566</v>
       </c>
       <c r="R38" t="n">
-        <v>7006716</v>
+        <v>7006630</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5582,6 +5577,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5598,22 +5598,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361119</v>
+        <v>122361219</v>
       </c>
       <c r="B2" t="n">
-        <v>79741</v>
+        <v>79742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494460</v>
+        <v>494464</v>
       </c>
       <c r="R2" t="n">
-        <v>7006357</v>
+        <v>7006354</v>
       </c>
       <c r="S2" t="n">
         <v>7</v>
@@ -760,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +789,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360490</v>
+        <v>122364212</v>
       </c>
       <c r="B3" t="n">
-        <v>79770</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,46 +824,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494402</v>
+        <v>494582</v>
       </c>
       <c r="R3" t="n">
-        <v>7006360</v>
+        <v>7006726</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,6 +902,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack några meter upp på en granstam.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -909,24 +921,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,7 +961,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122364212</v>
+        <v>122364729</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -992,14 +1009,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494582</v>
+        <v>494499</v>
       </c>
       <c r="R4" t="n">
-        <v>7006726</v>
+        <v>7006492</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1036,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
+          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,7 +1072,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad skog men inslag av tall, björk, sälg och asp. Här finns gott om stående och liggande död ved.</t>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1093,10 +1110,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122357863</v>
+        <v>122355933</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,51 +1126,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494497</v>
+        <v>494462</v>
       </c>
       <c r="R5" t="n">
-        <v>7006523</v>
+        <v>7006583</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1197,6 +1200,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1214,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122355540</v>
+        <v>122359111</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,37 +1253,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494535</v>
+        <v>494496</v>
       </c>
       <c r="R6" t="n">
-        <v>7006574</v>
+        <v>7006482</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1292,6 +1325,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår i stående död tall.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1308,22 +1346,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1341,10 +1379,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122360500</v>
+        <v>122357658</v>
       </c>
       <c r="B7" t="n">
-        <v>79777</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,31 +1391,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1386,10 +1429,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494402</v>
+        <v>494515</v>
       </c>
       <c r="R7" t="n">
-        <v>7006360</v>
+        <v>7006545</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,6 +1467,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hackspår och födosökspår med avskalad bark.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1440,22 +1488,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,10 +1521,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122360161</v>
+        <v>122360500</v>
       </c>
       <c r="B8" t="n">
-        <v>79741</v>
+        <v>79777</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1485,41 +1533,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494380</v>
+        <v>494402</v>
       </c>
       <c r="R8" t="n">
-        <v>7006419</v>
+        <v>7006360</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1549,11 +1602,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1605,10 +1653,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122354497</v>
+        <v>122360218</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1621,47 +1669,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494602</v>
+        <v>494394</v>
       </c>
       <c r="R9" t="n">
-        <v>7006702</v>
+        <v>7006412</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1693,11 +1731,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1724,12 +1757,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1747,10 +1780,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122357683</v>
+        <v>122355606</v>
       </c>
       <c r="B10" t="n">
-        <v>90855</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1763,39 +1796,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494501</v>
+        <v>494524</v>
       </c>
       <c r="R10" t="n">
-        <v>7006553</v>
+        <v>7006571</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1828,6 +1866,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hackspår/födosökspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1879,10 +1922,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122359691</v>
+        <v>122355822</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1895,37 +1938,47 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494410</v>
+        <v>494487</v>
       </c>
       <c r="R11" t="n">
-        <v>7006434</v>
+        <v>7006560</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1957,6 +2010,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1983,12 +2041,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2006,10 +2064,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122361005</v>
+        <v>122364537</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2022,37 +2080,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494444</v>
+        <v>494454</v>
       </c>
       <c r="R12" t="n">
-        <v>7006335</v>
+        <v>7006579</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2084,6 +2154,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2098,6 +2173,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2110,12 +2190,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2260,10 +2340,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122361219</v>
+        <v>122360161</v>
       </c>
       <c r="B14" t="n">
-        <v>79742</v>
+        <v>79741</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2276,42 +2356,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494464</v>
+        <v>494380</v>
       </c>
       <c r="R14" t="n">
-        <v>7006354</v>
+        <v>7006419</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2345,7 +2420,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2374,12 +2449,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2397,10 +2472,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122364537</v>
+        <v>122361274</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2413,49 +2488,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynjeflon, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494454</v>
+        <v>494472</v>
       </c>
       <c r="R15" t="n">
-        <v>7006579</v>
+        <v>7006382</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2489,7 +2552,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack några meter upp på en granstam med kådaflöden.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2506,11 +2569,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2523,12 +2581,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2546,10 +2604,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122359111</v>
+        <v>122357863</v>
       </c>
       <c r="B16" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2562,27 +2620,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2596,13 +2658,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494496</v>
+        <v>494497</v>
       </c>
       <c r="R16" t="n">
-        <v>7006482</v>
+        <v>7006523</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2634,11 +2696,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska hackspår/födosökspår i stående död tall.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2651,26 +2708,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2688,10 +2725,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122360599</v>
+        <v>122357683</v>
       </c>
       <c r="B17" t="n">
-        <v>79741</v>
+        <v>90855</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,34 +2741,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494411</v>
+        <v>494501</v>
       </c>
       <c r="R17" t="n">
-        <v>7006366</v>
+        <v>7006553</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2766,11 +2808,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2787,22 +2824,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2820,10 +2857,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122360113</v>
+        <v>122361037</v>
       </c>
       <c r="B18" t="n">
-        <v>79770</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2832,46 +2869,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494392</v>
+        <v>494456</v>
       </c>
       <c r="R18" t="n">
-        <v>7006448</v>
+        <v>7006360</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2919,22 +2951,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2952,10 +2984,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122357658</v>
+        <v>122361005</v>
       </c>
       <c r="B19" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2968,47 +3000,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494515</v>
+        <v>494444</v>
       </c>
       <c r="R19" t="n">
-        <v>7006545</v>
+        <v>7006335</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3040,11 +3062,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska hackspår och födosökspår med avskalad bark.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3071,12 +3088,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3094,10 +3111,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122355822</v>
+        <v>122355540</v>
       </c>
       <c r="B20" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3110,47 +3127,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494487</v>
+        <v>494535</v>
       </c>
       <c r="R20" t="n">
-        <v>7006560</v>
+        <v>7006574</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3182,11 +3189,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3213,12 +3215,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3236,10 +3238,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122361037</v>
+        <v>122361119</v>
       </c>
       <c r="B21" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3252,34 +3254,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494456</v>
+        <v>494460</v>
       </c>
       <c r="R21" t="n">
-        <v>7006360</v>
+        <v>7006357</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -3314,6 +3321,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal grov skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3330,22 +3342,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3363,10 +3375,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122355933</v>
+        <v>122360113</v>
       </c>
       <c r="B22" t="n">
-        <v>78660</v>
+        <v>79770</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3375,41 +3387,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494462</v>
+        <v>494392</v>
       </c>
       <c r="R22" t="n">
-        <v>7006583</v>
+        <v>7006448</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3457,22 +3474,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3490,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122355606</v>
+        <v>122364318</v>
       </c>
       <c r="B23" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3506,16 +3523,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3524,29 +3541,27 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494524</v>
+        <v>494511</v>
       </c>
       <c r="R23" t="n">
-        <v>7006571</v>
+        <v>7006626</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3580,7 +3595,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska hackspår/födosökspår.</t>
+          <t>Färska ringhack några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3597,6 +3612,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3609,12 +3629,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3753,10 +3773,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122360218</v>
+        <v>122360599</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3769,21 +3789,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3793,10 +3813,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494394</v>
+        <v>494411</v>
       </c>
       <c r="R25" t="n">
-        <v>7006412</v>
+        <v>7006366</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3831,6 +3851,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3847,22 +3872,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3880,10 +3905,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122361274</v>
+        <v>122354497</v>
       </c>
       <c r="B26" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3896,37 +3921,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494472</v>
+        <v>494602</v>
       </c>
       <c r="R26" t="n">
-        <v>7006382</v>
+        <v>7006702</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3960,7 +3995,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3989,12 +4024,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4012,10 +4047,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122364729</v>
+        <v>122360490</v>
       </c>
       <c r="B27" t="n">
-        <v>57384</v>
+        <v>79770</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4024,53 +4059,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494499</v>
+        <v>494402</v>
       </c>
       <c r="R27" t="n">
-        <v>7006492</v>
+        <v>7006360</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4102,11 +4130,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska inhack vid ca 2 meters höjd upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4121,29 +4144,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4161,10 +4179,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122364318</v>
+        <v>122359691</v>
       </c>
       <c r="B28" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4177,45 +4195,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494511</v>
+        <v>494410</v>
       </c>
       <c r="R28" t="n">
-        <v>7006626</v>
+        <v>7006434</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4247,11 +4257,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack några meter upp på en granstam.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4266,11 +4271,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall, björk, sälg och asp. Gott om stående och liggande död ved.</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122405719</v>
+        <v>122406373</v>
       </c>
       <c r="B29" t="n">
         <v>78660</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494740</v>
+        <v>494674</v>
       </c>
       <c r="R29" t="n">
-        <v>7006719</v>
+        <v>7006716</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122406373</v>
+        <v>122408149</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4449,34 +4449,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494674</v>
+        <v>494574</v>
       </c>
       <c r="R30" t="n">
-        <v>7006716</v>
+        <v>7006638</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4511,6 +4516,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4537,12 +4547,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4560,10 +4570,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122406150</v>
+        <v>122407432</v>
       </c>
       <c r="B31" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4576,34 +4586,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494722</v>
+        <v>494548</v>
       </c>
       <c r="R31" t="n">
-        <v>7006694</v>
+        <v>7006529</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4638,6 +4658,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4664,12 +4689,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4829,10 +4854,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122407432</v>
+        <v>122407975</v>
       </c>
       <c r="B33" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4845,44 +4870,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494548</v>
+        <v>494572</v>
       </c>
       <c r="R33" t="n">
-        <v>7006529</v>
+        <v>7006632</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4917,11 +4932,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4948,12 +4958,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5098,7 +5108,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122407975</v>
+        <v>122405719</v>
       </c>
       <c r="B35" t="n">
         <v>78660</v>
@@ -5138,10 +5148,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494572</v>
+        <v>494740</v>
       </c>
       <c r="R35" t="n">
-        <v>7006632</v>
+        <v>7006719</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5225,10 +5235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122406516</v>
+        <v>122407942</v>
       </c>
       <c r="B36" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5241,34 +5251,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494604</v>
+        <v>494566</v>
       </c>
       <c r="R36" t="n">
-        <v>7006665</v>
+        <v>7006630</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5303,6 +5323,11 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5319,22 +5344,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5352,10 +5377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122408149</v>
+        <v>122406516</v>
       </c>
       <c r="B37" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5368,39 +5393,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494574</v>
+        <v>494604</v>
       </c>
       <c r="R37" t="n">
-        <v>7006638</v>
+        <v>7006665</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5435,11 +5455,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5466,12 +5481,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5489,10 +5504,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122407942</v>
+        <v>122406150</v>
       </c>
       <c r="B38" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5505,44 +5520,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494566</v>
+        <v>494722</v>
       </c>
       <c r="R38" t="n">
-        <v>7006630</v>
+        <v>7006694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5577,11 +5582,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i stambasen av en stående död tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5598,22 +5598,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 60697-2024 artfynd.xlsx
+++ b/artfynd/A 60697-2024 artfynd.xlsx
@@ -4047,10 +4047,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122360490</v>
+        <v>122359691</v>
       </c>
       <c r="B27" t="n">
-        <v>79770</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4059,46 +4059,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494402</v>
+        <v>494410</v>
       </c>
       <c r="R27" t="n">
-        <v>7006360</v>
+        <v>7006434</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4146,22 +4141,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4179,10 +4174,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122359691</v>
+        <v>122360490</v>
       </c>
       <c r="B28" t="n">
-        <v>78660</v>
+        <v>79770</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4191,41 +4186,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494410</v>
+        <v>494402</v>
       </c>
       <c r="R28" t="n">
-        <v>7006434</v>
+        <v>7006360</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4273,22 +4273,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
